--- a/INPUT/inventario PT al 30-03-2026.xlsx
+++ b/INPUT/inventario PT al 30-03-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodrigom\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Downloads\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E25E0D-7B5C-4C94-AEA8-58A6F3FAED2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8961705-7AB9-49AB-8996-46A640B20E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E49F44D6-2AA4-4DB6-B5AA-2D3E646476D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{E49F44D6-2AA4-4DB6-B5AA-2D3E646476D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Marzo2026" sheetId="21" r:id="rId1"/>
@@ -29,12 +29,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -49,11 +45,20 @@
   <commentList>
     <comment ref="AF48" authorId="0" shapeId="0" xr:uid="{C87EF883-30C4-405A-828F-FD6A4F9A477E}">
       <text>
-        <t xml:space="preserve">[Comentario encadenado]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Salida por muestreo de calidad
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -68,11 +73,20 @@
   <commentList>
     <comment ref="AI46" authorId="0" shapeId="0" xr:uid="{C2EFD358-6160-43E1-8FDF-2161BD213BE5}">
       <text>
-        <t xml:space="preserve">[Comentario encadenado]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Salida por muestreo de calidad
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -87,11 +101,20 @@
   <commentList>
     <comment ref="Z45" authorId="0" shapeId="0" xr:uid="{53B486A3-A026-4DB1-B13F-7D075C5D5D9E}">
       <text>
-        <t xml:space="preserve">[Comentario encadenado]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Salida por muestreo de calidad
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -99,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="122">
   <si>
     <t>MATERIAL</t>
   </si>
@@ -463,6 +486,9 @@
   <si>
     <t>TM en Stock</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -473,7 +499,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -773,7 +799,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -912,32 +938,17 @@
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="11" fillId="12" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -946,8 +957,6 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="11" fillId="12" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -976,7 +985,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -987,6 +996,20 @@
     </xf>
     <xf numFmtId="9" fontId="10" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1317,11 +1340,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="TD"/>
       <sheetName val="Resumen"/>
@@ -2923,103 +2943,103 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BJ61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="37.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="3" customWidth="1"/>
     <col min="6" max="27" width="12" style="3" customWidth="1"/>
-    <col min="28" max="28" width="12.21875" style="3" customWidth="1"/>
-    <col min="29" max="29" width="1.109375" style="3" customWidth="1"/>
-    <col min="30" max="31" width="11.6640625" style="3" customWidth="1"/>
-    <col min="32" max="32" width="11.88671875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="12.6640625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="0.88671875" style="8" customWidth="1"/>
-    <col min="35" max="35" width="11.5546875" style="3" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="12.77734375" style="3" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="12.44140625" style="3" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="11.44140625" style="3" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="11.77734375" style="3" hidden="1" customWidth="1"/>
-    <col min="40" max="42" width="9.77734375" style="76" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="12.25" style="3" customWidth="1"/>
+    <col min="29" max="29" width="1.125" style="3" customWidth="1"/>
+    <col min="30" max="31" width="11.625" style="3" customWidth="1"/>
+    <col min="32" max="32" width="11.875" style="3" customWidth="1"/>
+    <col min="33" max="33" width="12.625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="0.875" style="8" customWidth="1"/>
+    <col min="35" max="35" width="11.5" style="3" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="12.75" style="3" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5" style="3" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="11.5" style="3" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="11.75" style="3" hidden="1" customWidth="1"/>
+    <col min="40" max="42" width="9.75" style="76" hidden="1" customWidth="1"/>
     <col min="43" max="43" width="0" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="9.77734375" style="3" customWidth="1"/>
-    <col min="45" max="47" width="9.77734375" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="12.44140625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="49" max="49" width="12.44140625" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="50" max="50" width="14.5546875" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="9.75" style="3" customWidth="1"/>
+    <col min="45" max="47" width="9.75" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="12.5" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="49" max="49" width="12.5" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="14.5" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="51" max="52" width="0" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="53" max="53" width="13.6640625" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="54" width="12.77734375" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="13.33203125" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="56" max="56" width="19.109375" style="3" customWidth="1" collapsed="1"/>
-    <col min="57" max="57" width="22.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="6.33203125" style="101" customWidth="1"/>
-    <col min="59" max="59" width="17.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="14.88671875" style="3" customWidth="1"/>
-    <col min="61" max="61" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="63" max="16384" width="11.5546875" style="3"/>
+    <col min="53" max="53" width="13.625" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="54" width="12.75" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="13.375" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="56" max="56" width="19.125" style="3" customWidth="1" collapsed="1"/>
+    <col min="57" max="57" width="22.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="6.375" style="3" customWidth="1"/>
+    <col min="59" max="59" width="17.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="14.875" style="3" customWidth="1"/>
+    <col min="61" max="61" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="63" max="16384" width="11.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:62" ht="15" thickBot="1">
+      <c r="A1" s="129" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="98" t="s">
+      <c r="C1" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AD1" s="98" t="s">
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="129"/>
+      <c r="AD1" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="AE1" s="98"/>
-      <c r="AF1" s="98"/>
-      <c r="AG1" s="98"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
       <c r="AI1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AJ1" s="94" t="s">
+      <c r="AJ1" s="125" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="98"/>
+    <row r="2" spans="1:62" ht="15" thickBot="1">
+      <c r="A2" s="129"/>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="98"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
@@ -3110,7 +3130,7 @@
       <c r="AI2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="AJ2" s="95"/>
+      <c r="AJ2" s="126"/>
       <c r="AK2" s="65" t="s">
         <v>75</v>
       </c>
@@ -3129,54 +3149,54 @@
       <c r="AT2" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="100" t="s">
+      <c r="AU2" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="AV2" s="126" t="s">
+      <c r="AV2" s="117" t="s">
         <v>120</v>
       </c>
-      <c r="AW2" s="127" t="s">
+      <c r="AW2" s="118" t="s">
         <v>107</v>
       </c>
-      <c r="AX2" s="127" t="s">
+      <c r="AX2" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="AY2" s="127" t="s">
+      <c r="AY2" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="AZ2" s="127" t="s">
+      <c r="AZ2" s="118" t="s">
         <v>110</v>
       </c>
-      <c r="BA2" s="127" t="s">
+      <c r="BA2" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="BB2" s="127" t="s">
+      <c r="BB2" s="118" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="128" t="s">
+      <c r="BC2" s="119" t="s">
         <v>112</v>
       </c>
-      <c r="BD2" s="129" t="s">
+      <c r="BD2" s="120" t="s">
         <v>116</v>
       </c>
-      <c r="BE2" s="129" t="s">
+      <c r="BE2" s="120" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="130"/>
-      <c r="BG2" s="131" t="s">
+      <c r="BF2" s="121"/>
+      <c r="BG2" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="BH2" s="132" t="s">
+      <c r="BH2" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="BI2" s="131" t="s">
+      <c r="BI2" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="BJ2" s="133" t="s">
+      <c r="BJ2" s="124" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -3262,63 +3282,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT3,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.73</v>
       </c>
-      <c r="AV3" s="102">
+      <c r="AV3" s="95">
         <f t="shared" ref="AV3:AV46" si="3">IF(ISERROR(AU3),0,AG3/1000)</f>
         <v>0.62</v>
       </c>
-      <c r="AW3" s="103">
+      <c r="AW3" s="96">
         <f t="shared" ref="AW3:AW46" si="4">IFERROR(AU3*AV3,0)*1000</f>
         <v>1072.5999999999999</v>
       </c>
-      <c r="AX3" s="104">
+      <c r="AX3" s="97">
         <f t="shared" ref="AX3:AX46" si="5">182*AV3</f>
         <v>112.84</v>
       </c>
-      <c r="AY3" s="103">
+      <c r="AY3" s="96">
         <f t="shared" ref="AY3:AY46" si="6">$AY$48/$AV$48*AV3</f>
         <v>22.733106630318151</v>
       </c>
-      <c r="AZ3" s="103">
+      <c r="AZ3" s="96">
         <f>$AZ$48/$AV$48*AV3</f>
         <v>51.468529781811014</v>
       </c>
-      <c r="BA3" s="103">
+      <c r="BA3" s="96">
         <f>$BA$48/$AV$48*AV3</f>
         <v>43.030360502870025</v>
       </c>
-      <c r="BB3" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC3" s="105">
+      <c r="BB3" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="98">
         <f>$BC$48</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="114">
+      <c r="BD3" s="105">
         <f>AW3+AX3+AY3+AZ3</f>
         <v>1259.6416364121289</v>
       </c>
-      <c r="BE3" s="115">
+      <c r="BE3" s="106">
         <f>IFERROR(BD3/AV3,0)</f>
         <v>2031.6800587292403</v>
       </c>
-      <c r="BF3" s="106"/>
-      <c r="BG3" s="116">
+      <c r="BF3" s="99"/>
+      <c r="BG3" s="107">
         <v>2200</v>
       </c>
-      <c r="BH3" s="107">
+      <c r="BH3" s="100">
         <f t="shared" ref="BH3:BH46" si="7">BG3*AV3</f>
         <v>1364</v>
       </c>
-      <c r="BI3" s="117">
+      <c r="BI3" s="108">
         <f>BH3-BD3</f>
         <v>104.35836358787105</v>
       </c>
-      <c r="BJ3" s="108">
+      <c r="BJ3" s="101">
         <f t="shared" ref="BJ3:BJ48" si="8">IFERROR(BI3/BH3,0)</f>
         <v>7.6509064213981709E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62">
       <c r="A4" s="17">
         <f>+A3+1</f>
         <v>2</v>
@@ -3456,63 +3476,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT4,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.73</v>
       </c>
-      <c r="AV4" s="102">
+      <c r="AV4" s="95">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="AW4" s="103">
+      <c r="AW4" s="96">
         <f t="shared" si="4"/>
         <v>48440</v>
       </c>
-      <c r="AX4" s="104">
+      <c r="AX4" s="97">
         <f t="shared" si="5"/>
         <v>5096</v>
       </c>
-      <c r="AY4" s="103">
+      <c r="AY4" s="96">
         <f t="shared" si="6"/>
         <v>1026.656428465981</v>
       </c>
-      <c r="AZ4" s="103">
+      <c r="AZ4" s="96">
         <f t="shared" ref="AZ4:AZ46" si="12">$AZ$48/$AV$48*AV4</f>
         <v>2324.3852159527555</v>
       </c>
-      <c r="BA4" s="103">
+      <c r="BA4" s="96">
         <f t="shared" ref="BA4:BA46" si="13">$BA$48/$AV$48*AV4</f>
         <v>1943.3066033554205</v>
       </c>
-      <c r="BB4" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC4" s="105">
+      <c r="BB4" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="98">
         <f t="shared" ref="BC4:BC46" si="14">$BC$48</f>
         <v>0</v>
       </c>
-      <c r="BD4" s="114">
+      <c r="BD4" s="105">
         <f t="shared" ref="BD4:BD46" si="15">AW4+AX4+AY4+AZ4</f>
         <v>56887.041644418736</v>
       </c>
-      <c r="BE4" s="115">
+      <c r="BE4" s="106">
         <f t="shared" ref="BE4:BE46" si="16">IFERROR(BD4/AV4,0)</f>
         <v>2031.6800587292405</v>
       </c>
-      <c r="BF4" s="106"/>
-      <c r="BG4" s="116">
+      <c r="BF4" s="99"/>
+      <c r="BG4" s="107">
         <v>2200</v>
       </c>
-      <c r="BH4" s="107">
+      <c r="BH4" s="100">
         <f t="shared" si="7"/>
         <v>61600</v>
       </c>
-      <c r="BI4" s="117">
+      <c r="BI4" s="108">
         <f t="shared" ref="BI4:BI46" si="17">BH4-BD4</f>
         <v>4712.9583555812642</v>
       </c>
-      <c r="BJ4" s="108">
+      <c r="BJ4" s="101">
         <f t="shared" si="8"/>
         <v>7.6509064213981556E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62">
       <c r="A5" s="17">
         <f t="shared" ref="A5:A32" si="18">+A4+1</f>
         <v>3</v>
@@ -3585,6 +3605,9 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
+      <c r="AR5" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="AS5" s="3">
         <v>10009178</v>
       </c>
@@ -3596,63 +3619,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT5,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.73</v>
       </c>
-      <c r="AV5" s="102">
+      <c r="AV5" s="95">
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="AW5" s="103">
+      <c r="AW5" s="96">
         <f t="shared" si="4"/>
         <v>1176.4000000000001</v>
       </c>
-      <c r="AX5" s="104">
+      <c r="AX5" s="97">
         <f t="shared" si="5"/>
         <v>123.76</v>
       </c>
-      <c r="AY5" s="103">
+      <c r="AY5" s="96">
         <f t="shared" si="6"/>
         <v>24.933084691316683</v>
       </c>
-      <c r="AZ5" s="103">
+      <c r="AZ5" s="96">
         <f t="shared" si="12"/>
         <v>56.449355244566917</v>
       </c>
-      <c r="BA5" s="103">
+      <c r="BA5" s="96">
         <f t="shared" si="13"/>
         <v>47.194588938631647</v>
       </c>
-      <c r="BB5" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC5" s="105">
+      <c r="BB5" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD5" s="114">
+      <c r="BD5" s="105">
         <f t="shared" si="15"/>
         <v>1381.5424399358837</v>
       </c>
-      <c r="BE5" s="115">
+      <c r="BE5" s="106">
         <f t="shared" si="16"/>
         <v>2031.6800587292407</v>
       </c>
-      <c r="BF5" s="106"/>
-      <c r="BG5" s="116">
+      <c r="BF5" s="99"/>
+      <c r="BG5" s="107">
         <v>2200</v>
       </c>
-      <c r="BH5" s="107">
+      <c r="BH5" s="100">
         <f t="shared" si="7"/>
         <v>1496</v>
       </c>
-      <c r="BI5" s="117">
+      <c r="BI5" s="108">
         <f t="shared" si="17"/>
         <v>114.45756006411625</v>
       </c>
-      <c r="BJ5" s="108">
+      <c r="BJ5" s="101">
         <f t="shared" si="8"/>
         <v>7.6509064213981445E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62">
       <c r="A6" s="17">
         <f t="shared" si="18"/>
         <v>4</v>
@@ -3734,63 +3757,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT6,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.73</v>
       </c>
-      <c r="AV6" s="102">
+      <c r="AV6" s="95">
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="AW6" s="103">
+      <c r="AW6" s="96">
         <f t="shared" si="4"/>
         <v>1176.4000000000001</v>
       </c>
-      <c r="AX6" s="104">
+      <c r="AX6" s="97">
         <f t="shared" si="5"/>
         <v>123.76</v>
       </c>
-      <c r="AY6" s="103">
+      <c r="AY6" s="96">
         <f t="shared" si="6"/>
         <v>24.933084691316683</v>
       </c>
-      <c r="AZ6" s="103">
+      <c r="AZ6" s="96">
         <f t="shared" si="12"/>
         <v>56.449355244566917</v>
       </c>
-      <c r="BA6" s="103">
+      <c r="BA6" s="96">
         <f t="shared" si="13"/>
         <v>47.194588938631647</v>
       </c>
-      <c r="BB6" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="105">
+      <c r="BB6" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD6" s="114">
+      <c r="BD6" s="105">
         <f t="shared" si="15"/>
         <v>1381.5424399358837</v>
       </c>
-      <c r="BE6" s="115">
+      <c r="BE6" s="106">
         <f t="shared" si="16"/>
         <v>2031.6800587292407</v>
       </c>
-      <c r="BF6" s="106"/>
-      <c r="BG6" s="116">
+      <c r="BF6" s="99"/>
+      <c r="BG6" s="107">
         <v>2200</v>
       </c>
-      <c r="BH6" s="107">
+      <c r="BH6" s="100">
         <f t="shared" si="7"/>
         <v>1496</v>
       </c>
-      <c r="BI6" s="117">
+      <c r="BI6" s="108">
         <f t="shared" si="17"/>
         <v>114.45756006411625</v>
       </c>
-      <c r="BJ6" s="108">
+      <c r="BJ6" s="101">
         <f t="shared" si="8"/>
         <v>7.6509064213981445E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62">
       <c r="A7" s="17">
         <f t="shared" si="18"/>
         <v>5</v>
@@ -3928,63 +3951,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT7,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.64</v>
       </c>
-      <c r="AV7" s="102">
+      <c r="AV7" s="95">
         <f t="shared" si="3"/>
         <v>253.24</v>
       </c>
-      <c r="AW7" s="103">
+      <c r="AW7" s="96">
         <f t="shared" si="4"/>
         <v>415313.60000000003</v>
       </c>
-      <c r="AX7" s="104">
+      <c r="AX7" s="97">
         <f t="shared" si="5"/>
         <v>46089.68</v>
       </c>
-      <c r="AY7" s="103">
+      <c r="AY7" s="96">
         <f t="shared" si="6"/>
         <v>9285.3740694544667</v>
       </c>
-      <c r="AZ7" s="103">
+      <c r="AZ7" s="96">
         <f t="shared" si="12"/>
         <v>21022.404003138421</v>
       </c>
-      <c r="BA7" s="103">
+      <c r="BA7" s="96">
         <f t="shared" si="13"/>
         <v>17575.820151204527</v>
       </c>
-      <c r="BB7" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC7" s="105">
+      <c r="BB7" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD7" s="114">
+      <c r="BD7" s="105">
         <f t="shared" si="15"/>
         <v>491711.05807259289</v>
       </c>
-      <c r="BE7" s="115">
+      <c r="BE7" s="106">
         <f t="shared" si="16"/>
         <v>1941.6800587292405</v>
       </c>
-      <c r="BF7" s="106"/>
-      <c r="BG7" s="116">
+      <c r="BF7" s="99"/>
+      <c r="BG7" s="107">
         <v>2200</v>
       </c>
-      <c r="BH7" s="107">
+      <c r="BH7" s="100">
         <f t="shared" si="7"/>
         <v>557128</v>
       </c>
-      <c r="BI7" s="117">
+      <c r="BI7" s="108">
         <f t="shared" si="17"/>
         <v>65416.941927407112</v>
       </c>
-      <c r="BJ7" s="108">
+      <c r="BJ7" s="101">
         <f t="shared" si="8"/>
         <v>0.11741815512307245</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62">
       <c r="A8" s="17">
         <f t="shared" si="18"/>
         <v>6</v>
@@ -4066,63 +4089,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT8,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.87</v>
       </c>
-      <c r="AV8" s="102">
+      <c r="AV8" s="95">
         <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="AW8" s="103">
+      <c r="AW8" s="96">
         <f t="shared" si="4"/>
         <v>224.4</v>
       </c>
-      <c r="AX8" s="104">
+      <c r="AX8" s="97">
         <f t="shared" si="5"/>
         <v>21.84</v>
       </c>
-      <c r="AY8" s="103">
+      <c r="AY8" s="96">
         <f t="shared" si="6"/>
         <v>4.3999561219970618</v>
       </c>
-      <c r="AZ8" s="103">
+      <c r="AZ8" s="96">
         <f t="shared" si="12"/>
         <v>9.9616509255118082</v>
       </c>
-      <c r="BA8" s="103">
+      <c r="BA8" s="96">
         <f t="shared" si="13"/>
         <v>8.3284568715232297</v>
       </c>
-      <c r="BB8" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC8" s="105">
+      <c r="BB8" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD8" s="114">
+      <c r="BD8" s="105">
         <f t="shared" si="15"/>
         <v>260.60160704750888</v>
       </c>
-      <c r="BE8" s="115">
+      <c r="BE8" s="106">
         <f t="shared" si="16"/>
         <v>2171.680058729241</v>
       </c>
-      <c r="BF8" s="106"/>
-      <c r="BG8" s="116">
+      <c r="BF8" s="99"/>
+      <c r="BG8" s="107">
         <v>2200</v>
       </c>
-      <c r="BH8" s="107">
+      <c r="BH8" s="100">
         <f t="shared" si="7"/>
         <v>264</v>
       </c>
-      <c r="BI8" s="117">
+      <c r="BI8" s="108">
         <f t="shared" si="17"/>
         <v>3.3983929524911218</v>
       </c>
-      <c r="BJ8" s="108">
+      <c r="BJ8" s="101">
         <f t="shared" si="8"/>
         <v>1.2872700577617885E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62">
       <c r="A9" s="17">
         <f t="shared" si="18"/>
         <v>7</v>
@@ -4203,61 +4226,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT9,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV9" s="102">
+      <c r="AV9" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW9" s="103">
+      <c r="AW9" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX9" s="104">
+      <c r="AX9" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY9" s="103">
+      <c r="AY9" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ9" s="103">
+      <c r="AZ9" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA9" s="103">
+      <c r="BA9" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC9" s="105">
+      <c r="BB9" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD9" s="114">
+      <c r="BD9" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE9" s="115">
+      <c r="BE9" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF9" s="106"/>
-      <c r="BG9" s="116"/>
-      <c r="BH9" s="107">
+      <c r="BF9" s="99"/>
+      <c r="BG9" s="107"/>
+      <c r="BH9" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI9" s="117">
+      <c r="BI9" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ9" s="108">
+      <c r="BJ9" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62">
       <c r="A10" s="17"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39" t="s">
@@ -4331,61 +4354,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT10,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV10" s="102">
+      <c r="AV10" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW10" s="103">
+      <c r="AW10" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX10" s="104">
+      <c r="AX10" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY10" s="103">
+      <c r="AY10" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ10" s="103">
+      <c r="AZ10" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA10" s="103">
+      <c r="BA10" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC10" s="105">
+      <c r="BB10" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD10" s="114">
+      <c r="BD10" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE10" s="115">
+      <c r="BE10" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF10" s="106"/>
-      <c r="BG10" s="116"/>
-      <c r="BH10" s="107">
+      <c r="BF10" s="99"/>
+      <c r="BG10" s="107"/>
+      <c r="BH10" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI10" s="117">
+      <c r="BI10" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ10" s="108">
+      <c r="BJ10" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62">
       <c r="A11" s="17"/>
       <c r="B11" s="39"/>
       <c r="C11" s="39" t="s">
@@ -4461,61 +4484,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT11,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV11" s="102">
+      <c r="AV11" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW11" s="103">
+      <c r="AW11" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX11" s="104">
+      <c r="AX11" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY11" s="103">
+      <c r="AY11" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ11" s="103">
+      <c r="AZ11" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA11" s="103">
+      <c r="BA11" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="105">
+      <c r="BB11" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD11" s="114">
+      <c r="BD11" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE11" s="115">
+      <c r="BE11" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF11" s="106"/>
-      <c r="BG11" s="116"/>
-      <c r="BH11" s="107">
+      <c r="BF11" s="99"/>
+      <c r="BG11" s="107"/>
+      <c r="BH11" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="117">
+      <c r="BI11" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ11" s="108">
+      <c r="BJ11" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" s="8" customFormat="1">
       <c r="A12" s="37">
         <v>8</v>
       </c>
@@ -4635,61 +4658,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT12,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV12" s="102">
+      <c r="AV12" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW12" s="103">
+      <c r="AW12" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX12" s="104">
+      <c r="AX12" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY12" s="109">
+      <c r="AY12" s="102">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ12" s="103">
+      <c r="AZ12" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA12" s="103">
+      <c r="BA12" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="105">
+      <c r="BB12" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD12" s="114">
+      <c r="BD12" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE12" s="115">
+      <c r="BE12" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF12" s="106"/>
-      <c r="BG12" s="116"/>
-      <c r="BH12" s="107">
+      <c r="BF12" s="99"/>
+      <c r="BG12" s="107"/>
+      <c r="BH12" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI12" s="117">
+      <c r="BI12" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ12" s="108">
+      <c r="BJ12" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" s="8" customFormat="1">
       <c r="A13" s="37">
         <f>+A12+1</f>
         <v>9</v>
@@ -4816,63 +4839,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT13,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.4</v>
       </c>
-      <c r="AV13" s="102">
+      <c r="AV13" s="95">
         <f t="shared" si="3"/>
         <v>46.78</v>
       </c>
-      <c r="AW13" s="103">
+      <c r="AW13" s="96">
         <f t="shared" si="4"/>
         <v>65492.000000000007</v>
       </c>
-      <c r="AX13" s="104">
+      <c r="AX13" s="97">
         <f t="shared" si="5"/>
         <v>8513.9600000000009</v>
       </c>
-      <c r="AY13" s="109">
+      <c r="AY13" s="102">
         <f t="shared" si="6"/>
         <v>1715.2495615585212</v>
       </c>
-      <c r="AZ13" s="103">
+      <c r="AZ13" s="96">
         <f t="shared" si="12"/>
         <v>3883.3835857953536</v>
       </c>
-      <c r="BA13" s="103">
+      <c r="BA13" s="96">
         <f t="shared" si="13"/>
         <v>3246.7101037488064</v>
       </c>
-      <c r="BB13" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC13" s="105">
+      <c r="BB13" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD13" s="114">
+      <c r="BD13" s="105">
         <f t="shared" si="15"/>
         <v>79604.59314735388</v>
       </c>
-      <c r="BE13" s="115">
+      <c r="BE13" s="106">
         <f t="shared" si="16"/>
         <v>1701.6800587292407</v>
       </c>
-      <c r="BF13" s="106"/>
-      <c r="BG13" s="116">
+      <c r="BF13" s="99"/>
+      <c r="BG13" s="107">
         <v>1500</v>
       </c>
-      <c r="BH13" s="107">
+      <c r="BH13" s="100">
         <f t="shared" si="7"/>
         <v>70170</v>
       </c>
-      <c r="BI13" s="117">
+      <c r="BI13" s="108">
         <f t="shared" si="17"/>
         <v>-9434.5931473538803</v>
       </c>
-      <c r="BJ13" s="108">
+      <c r="BJ13" s="101">
         <f t="shared" si="8"/>
         <v>-0.13445337248616046</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62">
       <c r="A14" s="7">
         <f>+A13+1</f>
         <v>10</v>
@@ -4954,63 +4977,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT14,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.74</v>
       </c>
-      <c r="AV14" s="102">
+      <c r="AV14" s="95">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
-      <c r="AW14" s="103">
+      <c r="AW14" s="96">
         <f t="shared" si="4"/>
         <v>522</v>
       </c>
-      <c r="AX14" s="104">
+      <c r="AX14" s="97">
         <f t="shared" si="5"/>
         <v>54.6</v>
       </c>
-      <c r="AY14" s="103">
+      <c r="AY14" s="96">
         <f t="shared" si="6"/>
         <v>10.999890304992654</v>
       </c>
-      <c r="AZ14" s="103">
+      <c r="AZ14" s="96">
         <f t="shared" si="12"/>
         <v>24.904127313779522</v>
       </c>
-      <c r="BA14" s="103">
+      <c r="BA14" s="96">
         <f t="shared" si="13"/>
         <v>20.821142178808078</v>
       </c>
-      <c r="BB14" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC14" s="105">
+      <c r="BB14" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="114">
+      <c r="BD14" s="105">
         <f t="shared" si="15"/>
         <v>612.5040176187722</v>
       </c>
-      <c r="BE14" s="115">
+      <c r="BE14" s="106">
         <f t="shared" si="16"/>
         <v>2041.6800587292407</v>
       </c>
-      <c r="BF14" s="106"/>
-      <c r="BG14" s="116">
+      <c r="BF14" s="99"/>
+      <c r="BG14" s="107">
         <v>2200</v>
       </c>
-      <c r="BH14" s="107">
+      <c r="BH14" s="100">
         <f t="shared" si="7"/>
         <v>660</v>
       </c>
-      <c r="BI14" s="117">
+      <c r="BI14" s="108">
         <f t="shared" si="17"/>
         <v>47.495982381227805</v>
       </c>
-      <c r="BJ14" s="108">
+      <c r="BJ14" s="101">
         <f t="shared" si="8"/>
         <v>7.1963609668526982E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62">
       <c r="A15" s="7">
         <f t="shared" ref="A15:A17" si="20">+A14+1</f>
         <v>11</v>
@@ -5092,63 +5115,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT15,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.74</v>
       </c>
-      <c r="AV15" s="102">
+      <c r="AV15" s="95">
         <f t="shared" si="3"/>
         <v>1.1200000000000001</v>
       </c>
-      <c r="AW15" s="103">
+      <c r="AW15" s="96">
         <f t="shared" si="4"/>
         <v>1948.8000000000002</v>
       </c>
-      <c r="AX15" s="104">
+      <c r="AX15" s="97">
         <f t="shared" si="5"/>
         <v>203.84000000000003</v>
       </c>
-      <c r="AY15" s="103">
+      <c r="AY15" s="96">
         <f t="shared" si="6"/>
         <v>41.066257138639244</v>
       </c>
-      <c r="AZ15" s="103">
+      <c r="AZ15" s="96">
         <f t="shared" si="12"/>
         <v>92.975408638110224</v>
       </c>
-      <c r="BA15" s="103">
+      <c r="BA15" s="96">
         <f t="shared" si="13"/>
         <v>77.732264134216834</v>
       </c>
-      <c r="BB15" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC15" s="105">
+      <c r="BB15" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD15" s="114">
+      <c r="BD15" s="105">
         <f t="shared" si="15"/>
         <v>2286.6816657767499</v>
       </c>
-      <c r="BE15" s="115">
+      <c r="BE15" s="106">
         <f t="shared" si="16"/>
         <v>2041.6800587292407</v>
       </c>
-      <c r="BF15" s="106"/>
-      <c r="BG15" s="116">
+      <c r="BF15" s="99"/>
+      <c r="BG15" s="107">
         <v>2200</v>
       </c>
-      <c r="BH15" s="107">
+      <c r="BH15" s="100">
         <f t="shared" si="7"/>
         <v>2464.0000000000005</v>
       </c>
-      <c r="BI15" s="117">
+      <c r="BI15" s="108">
         <f t="shared" si="17"/>
         <v>177.31833422325053</v>
       </c>
-      <c r="BJ15" s="108">
+      <c r="BJ15" s="101">
         <f t="shared" si="8"/>
         <v>7.1963609668526982E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62">
       <c r="A16" s="7">
         <f t="shared" si="20"/>
         <v>12</v>
@@ -5286,63 +5309,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT16,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.74</v>
       </c>
-      <c r="AV16" s="102">
+      <c r="AV16" s="95">
         <f t="shared" si="3"/>
         <v>460.18</v>
       </c>
-      <c r="AW16" s="103">
+      <c r="AW16" s="96">
         <f t="shared" si="4"/>
         <v>800713.20000000007</v>
       </c>
-      <c r="AX16" s="104">
+      <c r="AX16" s="97">
         <f t="shared" si="5"/>
         <v>83752.759999999995</v>
       </c>
-      <c r="AY16" s="103">
+      <c r="AY16" s="96">
         <f t="shared" si="6"/>
         <v>16873.098401838397</v>
       </c>
-      <c r="AZ16" s="103">
+      <c r="AZ16" s="96">
         <f t="shared" si="12"/>
         <v>38201.271024183538</v>
       </c>
-      <c r="BA16" s="103">
+      <c r="BA16" s="96">
         <f t="shared" si="13"/>
         <v>31938.244026146338</v>
       </c>
-      <c r="BB16" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="105">
+      <c r="BB16" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD16" s="114">
+      <c r="BD16" s="105">
         <f t="shared" si="15"/>
         <v>939540.32942602201</v>
       </c>
-      <c r="BE16" s="115">
+      <c r="BE16" s="106">
         <f t="shared" si="16"/>
         <v>2041.6800587292407</v>
       </c>
-      <c r="BF16" s="106"/>
-      <c r="BG16" s="116">
+      <c r="BF16" s="99"/>
+      <c r="BG16" s="107">
         <v>2200</v>
       </c>
-      <c r="BH16" s="107">
+      <c r="BH16" s="100">
         <f t="shared" si="7"/>
         <v>1012396</v>
       </c>
-      <c r="BI16" s="117">
+      <c r="BI16" s="108">
         <f t="shared" si="17"/>
         <v>72855.670573977986</v>
       </c>
-      <c r="BJ16" s="108">
+      <c r="BJ16" s="101">
         <f t="shared" si="8"/>
         <v>7.1963609668526926E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62">
       <c r="A17" s="7">
         <f t="shared" si="20"/>
         <v>13</v>
@@ -5462,63 +5485,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT17,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.74</v>
       </c>
-      <c r="AV17" s="102">
+      <c r="AV17" s="95">
         <f t="shared" si="3"/>
         <v>118.7</v>
       </c>
-      <c r="AW17" s="103">
+      <c r="AW17" s="96">
         <f t="shared" si="4"/>
         <v>206538</v>
       </c>
-      <c r="AX17" s="104">
+      <c r="AX17" s="97">
         <f t="shared" si="5"/>
         <v>21603.4</v>
       </c>
-      <c r="AY17" s="103">
+      <c r="AY17" s="96">
         <f t="shared" si="6"/>
         <v>4352.2899306754271</v>
       </c>
-      <c r="AZ17" s="103">
+      <c r="AZ17" s="96">
         <f t="shared" si="12"/>
         <v>9853.733040485431</v>
       </c>
-      <c r="BA17" s="103">
+      <c r="BA17" s="96">
         <f t="shared" si="13"/>
         <v>8238.2319220817299</v>
       </c>
-      <c r="BB17" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC17" s="105">
+      <c r="BB17" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD17" s="114">
+      <c r="BD17" s="105">
         <f t="shared" si="15"/>
         <v>242347.42297116088</v>
       </c>
-      <c r="BE17" s="115">
+      <c r="BE17" s="106">
         <f t="shared" si="16"/>
         <v>2041.6800587292407</v>
       </c>
-      <c r="BF17" s="106"/>
-      <c r="BG17" s="116">
+      <c r="BF17" s="99"/>
+      <c r="BG17" s="107">
         <v>2200</v>
       </c>
-      <c r="BH17" s="107">
+      <c r="BH17" s="100">
         <f t="shared" si="7"/>
         <v>261140</v>
       </c>
-      <c r="BI17" s="117">
+      <c r="BI17" s="108">
         <f t="shared" si="17"/>
         <v>18792.577028839121</v>
       </c>
-      <c r="BJ17" s="108">
+      <c r="BJ17" s="101">
         <f t="shared" si="8"/>
         <v>7.1963609668526926E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62">
       <c r="A18" s="23">
         <f>+A17+1</f>
         <v>14</v>
@@ -5600,63 +5623,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT18,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.86</v>
       </c>
-      <c r="AV18" s="102">
+      <c r="AV18" s="95">
         <f t="shared" si="3"/>
         <v>0.94</v>
       </c>
-      <c r="AW18" s="103">
+      <c r="AW18" s="96">
         <f t="shared" si="4"/>
         <v>1748.3999999999999</v>
       </c>
-      <c r="AX18" s="104">
+      <c r="AX18" s="97">
         <f t="shared" si="5"/>
         <v>171.07999999999998</v>
       </c>
-      <c r="AY18" s="103">
+      <c r="AY18" s="96">
         <f t="shared" si="6"/>
         <v>34.466322955643648</v>
       </c>
-      <c r="AZ18" s="103">
+      <c r="AZ18" s="96">
         <f t="shared" si="12"/>
         <v>78.032932249842503</v>
       </c>
-      <c r="BA18" s="103">
+      <c r="BA18" s="96">
         <f t="shared" si="13"/>
         <v>65.239578826931975</v>
       </c>
-      <c r="BB18" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC18" s="105">
+      <c r="BB18" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="114">
+      <c r="BD18" s="105">
         <f t="shared" si="15"/>
         <v>2031.979255205486</v>
       </c>
-      <c r="BE18" s="115">
+      <c r="BE18" s="106">
         <f t="shared" si="16"/>
         <v>2161.6800587292405</v>
       </c>
-      <c r="BF18" s="106"/>
-      <c r="BG18" s="116">
+      <c r="BF18" s="99"/>
+      <c r="BG18" s="107">
         <v>1500</v>
       </c>
-      <c r="BH18" s="107">
+      <c r="BH18" s="100">
         <f t="shared" si="7"/>
         <v>1410</v>
       </c>
-      <c r="BI18" s="117">
+      <c r="BI18" s="108">
         <f t="shared" si="17"/>
         <v>-621.97925520548597</v>
       </c>
-      <c r="BJ18" s="108">
+      <c r="BJ18" s="101">
         <f t="shared" si="8"/>
         <v>-0.44112003915282694</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62">
       <c r="A19" s="23">
         <f t="shared" ref="A19:A23" si="21">+A18+1</f>
         <v>15</v>
@@ -5740,63 +5763,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT19,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.86</v>
       </c>
-      <c r="AV19" s="102">
+      <c r="AV19" s="95">
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AW19" s="103">
+      <c r="AW19" s="96">
         <f t="shared" si="4"/>
         <v>1041.6000000000001</v>
       </c>
-      <c r="AX19" s="104">
+      <c r="AX19" s="97">
         <f t="shared" si="5"/>
         <v>101.92000000000002</v>
       </c>
-      <c r="AY19" s="103">
+      <c r="AY19" s="96">
         <f t="shared" si="6"/>
         <v>20.533128569319622</v>
       </c>
-      <c r="AZ19" s="103">
+      <c r="AZ19" s="96">
         <f t="shared" si="12"/>
         <v>46.487704319055112</v>
       </c>
-      <c r="BA19" s="103">
+      <c r="BA19" s="96">
         <f t="shared" si="13"/>
         <v>38.866132067108417</v>
       </c>
-      <c r="BB19" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC19" s="105">
+      <c r="BB19" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="114">
+      <c r="BD19" s="105">
         <f t="shared" si="15"/>
         <v>1210.540832888375</v>
       </c>
-      <c r="BE19" s="115">
+      <c r="BE19" s="106">
         <f t="shared" si="16"/>
         <v>2161.680058729241</v>
       </c>
-      <c r="BF19" s="106"/>
-      <c r="BG19" s="116">
+      <c r="BF19" s="99"/>
+      <c r="BG19" s="107">
         <v>1500</v>
       </c>
-      <c r="BH19" s="107">
+      <c r="BH19" s="100">
         <f t="shared" si="7"/>
         <v>840.00000000000011</v>
       </c>
-      <c r="BI19" s="117">
+      <c r="BI19" s="108">
         <f t="shared" si="17"/>
         <v>-370.54083288837489</v>
       </c>
-      <c r="BJ19" s="108">
+      <c r="BJ19" s="101">
         <f t="shared" si="8"/>
         <v>-0.44112003915282721</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62">
       <c r="A20" s="23">
         <f t="shared" si="21"/>
         <v>16</v>
@@ -5935,63 +5958,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT20,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.86</v>
       </c>
-      <c r="AV20" s="102">
+      <c r="AV20" s="95">
         <f t="shared" si="3"/>
         <v>76.56</v>
       </c>
-      <c r="AW20" s="103">
+      <c r="AW20" s="96">
         <f t="shared" si="4"/>
         <v>142401.60000000001</v>
       </c>
-      <c r="AX20" s="104">
+      <c r="AX20" s="97">
         <f t="shared" si="5"/>
         <v>13933.92</v>
       </c>
-      <c r="AY20" s="103">
+      <c r="AY20" s="96">
         <f t="shared" si="6"/>
         <v>2807.1720058341252</v>
       </c>
-      <c r="AZ20" s="103">
+      <c r="AZ20" s="96">
         <f t="shared" si="12"/>
         <v>6355.5332904765337</v>
       </c>
-      <c r="BA20" s="103">
+      <c r="BA20" s="96">
         <f t="shared" si="13"/>
         <v>5313.5554840318218</v>
       </c>
-      <c r="BB20" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC20" s="105">
+      <c r="BB20" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD20" s="114">
+      <c r="BD20" s="105">
         <f t="shared" si="15"/>
         <v>165498.22529631067</v>
       </c>
-      <c r="BE20" s="115">
+      <c r="BE20" s="106">
         <f t="shared" si="16"/>
         <v>2161.6800587292405</v>
       </c>
-      <c r="BF20" s="106"/>
-      <c r="BG20" s="116">
+      <c r="BF20" s="99"/>
+      <c r="BG20" s="107">
         <v>1500</v>
       </c>
-      <c r="BH20" s="107">
+      <c r="BH20" s="100">
         <f t="shared" si="7"/>
         <v>114840</v>
       </c>
-      <c r="BI20" s="117">
+      <c r="BI20" s="108">
         <f t="shared" si="17"/>
         <v>-50658.225296310673</v>
       </c>
-      <c r="BJ20" s="108">
+      <c r="BJ20" s="101">
         <f t="shared" si="8"/>
         <v>-0.44112003915282716</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62">
       <c r="A21" s="23">
         <f t="shared" si="21"/>
         <v>17</v>
@@ -6117,63 +6140,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT21,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.86</v>
       </c>
-      <c r="AV21" s="102">
+      <c r="AV21" s="95">
         <f t="shared" si="3"/>
         <v>3.48</v>
       </c>
-      <c r="AW21" s="103">
+      <c r="AW21" s="96">
         <f t="shared" si="4"/>
         <v>6472.8</v>
       </c>
-      <c r="AX21" s="104">
+      <c r="AX21" s="97">
         <f t="shared" si="5"/>
         <v>633.36</v>
       </c>
-      <c r="AY21" s="103">
+      <c r="AY21" s="96">
         <f t="shared" si="6"/>
         <v>127.59872753791478</v>
       </c>
-      <c r="AZ21" s="103">
+      <c r="AZ21" s="96">
         <f t="shared" si="12"/>
         <v>288.88787683984248</v>
       </c>
-      <c r="BA21" s="103">
+      <c r="BA21" s="96">
         <f t="shared" si="13"/>
         <v>241.52524927417369</v>
       </c>
-      <c r="BB21" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC21" s="105">
+      <c r="BB21" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD21" s="114">
+      <c r="BD21" s="105">
         <f t="shared" si="15"/>
         <v>7522.6466043777573</v>
       </c>
-      <c r="BE21" s="115">
+      <c r="BE21" s="106">
         <f t="shared" si="16"/>
         <v>2161.6800587292405</v>
       </c>
-      <c r="BF21" s="106"/>
-      <c r="BG21" s="116">
+      <c r="BF21" s="99"/>
+      <c r="BG21" s="107">
         <v>1500</v>
       </c>
-      <c r="BH21" s="107">
+      <c r="BH21" s="100">
         <f t="shared" si="7"/>
         <v>5220</v>
       </c>
-      <c r="BI21" s="117">
+      <c r="BI21" s="108">
         <f t="shared" si="17"/>
         <v>-2302.6466043777573</v>
       </c>
-      <c r="BJ21" s="108">
+      <c r="BJ21" s="101">
         <f t="shared" si="8"/>
         <v>-0.44112003915282705</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62">
       <c r="A22" s="23">
         <f t="shared" si="21"/>
         <v>18</v>
@@ -6310,63 +6333,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT22,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.86</v>
       </c>
-      <c r="AV22" s="102">
+      <c r="AV22" s="95">
         <f t="shared" si="3"/>
         <v>53.5</v>
       </c>
-      <c r="AW22" s="103">
+      <c r="AW22" s="96">
         <f t="shared" si="4"/>
         <v>99510</v>
       </c>
-      <c r="AX22" s="104">
+      <c r="AX22" s="97">
         <f t="shared" si="5"/>
         <v>9737</v>
       </c>
-      <c r="AY22" s="103">
+      <c r="AY22" s="96">
         <f t="shared" si="6"/>
         <v>1961.6471043903566</v>
       </c>
-      <c r="AZ22" s="103">
+      <c r="AZ22" s="96">
         <f t="shared" si="12"/>
         <v>4441.2360376240149</v>
       </c>
-      <c r="BA22" s="103">
+      <c r="BA22" s="96">
         <f t="shared" si="13"/>
         <v>3713.1036885541071</v>
       </c>
-      <c r="BB22" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC22" s="105">
+      <c r="BB22" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD22" s="114">
+      <c r="BD22" s="105">
         <f t="shared" si="15"/>
         <v>115649.88314201437</v>
       </c>
-      <c r="BE22" s="115">
+      <c r="BE22" s="106">
         <f t="shared" si="16"/>
         <v>2161.6800587292405</v>
       </c>
-      <c r="BF22" s="106"/>
-      <c r="BG22" s="116">
+      <c r="BF22" s="99"/>
+      <c r="BG22" s="107">
         <v>1500</v>
       </c>
-      <c r="BH22" s="107">
+      <c r="BH22" s="100">
         <f t="shared" si="7"/>
         <v>80250</v>
       </c>
-      <c r="BI22" s="117">
+      <c r="BI22" s="108">
         <f t="shared" si="17"/>
         <v>-35399.883142014369</v>
       </c>
-      <c r="BJ22" s="108">
+      <c r="BJ22" s="101">
         <f t="shared" si="8"/>
         <v>-0.44112003915282705</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62">
       <c r="A23" s="23">
         <f t="shared" si="21"/>
         <v>19</v>
@@ -6487,61 +6510,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT23,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV23" s="102">
+      <c r="AV23" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW23" s="103">
+      <c r="AW23" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX23" s="104">
+      <c r="AX23" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY23" s="103">
+      <c r="AY23" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ23" s="103">
+      <c r="AZ23" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA23" s="103">
+      <c r="BA23" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC23" s="105">
+      <c r="BB23" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD23" s="114">
+      <c r="BD23" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="115">
+      <c r="BE23" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF23" s="106"/>
-      <c r="BG23" s="116"/>
-      <c r="BH23" s="107">
+      <c r="BF23" s="99"/>
+      <c r="BG23" s="107"/>
+      <c r="BH23" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI23" s="117">
+      <c r="BI23" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ23" s="108">
+      <c r="BJ23" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" s="8" customFormat="1">
       <c r="A24" s="11">
         <f>+A23+1</f>
         <v>20</v>
@@ -6673,63 +6696,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT24,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.7</v>
       </c>
-      <c r="AV24" s="102">
+      <c r="AV24" s="95">
         <f t="shared" si="3"/>
         <v>105.2</v>
       </c>
-      <c r="AW24" s="103">
+      <c r="AW24" s="96">
         <f t="shared" si="4"/>
         <v>178840</v>
       </c>
-      <c r="AX24" s="104">
+      <c r="AX24" s="97">
         <f t="shared" si="5"/>
         <v>19146.400000000001</v>
       </c>
-      <c r="AY24" s="109">
+      <c r="AY24" s="102">
         <f t="shared" si="6"/>
         <v>3857.2948669507573</v>
       </c>
-      <c r="AZ24" s="103">
+      <c r="AZ24" s="96">
         <f t="shared" si="12"/>
         <v>8733.0473113653516</v>
       </c>
-      <c r="BA24" s="103">
+      <c r="BA24" s="96">
         <f t="shared" si="13"/>
         <v>7301.2805240353655</v>
       </c>
-      <c r="BB24" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC24" s="105">
+      <c r="BB24" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC24" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD24" s="114">
+      <c r="BD24" s="105">
         <f t="shared" si="15"/>
         <v>210576.74217831608</v>
       </c>
-      <c r="BE24" s="115">
+      <c r="BE24" s="106">
         <f t="shared" si="16"/>
         <v>2001.6800587292403</v>
       </c>
-      <c r="BF24" s="106"/>
-      <c r="BG24" s="116">
+      <c r="BF24" s="99"/>
+      <c r="BG24" s="107">
         <v>2900</v>
       </c>
-      <c r="BH24" s="107">
+      <c r="BH24" s="100">
         <f t="shared" si="7"/>
         <v>305080</v>
       </c>
-      <c r="BI24" s="117">
+      <c r="BI24" s="108">
         <f t="shared" si="17"/>
         <v>94503.257821683917</v>
       </c>
-      <c r="BJ24" s="108">
+      <c r="BJ24" s="101">
         <f t="shared" si="8"/>
         <v>0.30976549698991712</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62">
       <c r="A25" s="11">
         <f t="shared" ref="A25:A30" si="22">+A24+1</f>
         <v>21</v>
@@ -6813,63 +6836,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT25,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.72</v>
       </c>
-      <c r="AV25" s="102">
+      <c r="AV25" s="95">
         <f t="shared" si="3"/>
         <v>0.36</v>
       </c>
-      <c r="AW25" s="103">
+      <c r="AW25" s="96">
         <f t="shared" si="4"/>
         <v>619.19999999999993</v>
       </c>
-      <c r="AX25" s="104">
+      <c r="AX25" s="97">
         <f t="shared" si="5"/>
         <v>65.52</v>
       </c>
-      <c r="AY25" s="103">
+      <c r="AY25" s="96">
         <f t="shared" si="6"/>
         <v>13.199868365991184</v>
       </c>
-      <c r="AZ25" s="103">
+      <c r="AZ25" s="96">
         <f t="shared" si="12"/>
         <v>29.884952776535425</v>
       </c>
-      <c r="BA25" s="103">
+      <c r="BA25" s="96">
         <f t="shared" si="13"/>
         <v>24.985370614569693</v>
       </c>
-      <c r="BB25" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC25" s="105">
+      <c r="BB25" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC25" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD25" s="114">
+      <c r="BD25" s="105">
         <f t="shared" si="15"/>
         <v>727.80482114252652</v>
       </c>
-      <c r="BE25" s="115">
+      <c r="BE25" s="106">
         <f t="shared" si="16"/>
         <v>2021.6800587292405</v>
       </c>
-      <c r="BF25" s="106"/>
-      <c r="BG25" s="116">
+      <c r="BF25" s="99"/>
+      <c r="BG25" s="107">
         <v>2900</v>
       </c>
-      <c r="BH25" s="107">
+      <c r="BH25" s="100">
         <f t="shared" si="7"/>
         <v>1044</v>
       </c>
-      <c r="BI25" s="117">
+      <c r="BI25" s="108">
         <f t="shared" si="17"/>
         <v>316.19517885747348</v>
       </c>
-      <c r="BJ25" s="108">
+      <c r="BJ25" s="101">
         <f t="shared" si="8"/>
         <v>0.30286894526577918</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62">
       <c r="A26" s="11">
         <f t="shared" si="22"/>
         <v>22</v>
@@ -6995,63 +7018,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT26,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.72</v>
       </c>
-      <c r="AV26" s="102">
+      <c r="AV26" s="95">
         <f t="shared" si="3"/>
         <v>10.86</v>
       </c>
-      <c r="AW26" s="103">
+      <c r="AW26" s="96">
         <f t="shared" si="4"/>
         <v>18679.199999999997</v>
       </c>
-      <c r="AX26" s="104">
+      <c r="AX26" s="97">
         <f t="shared" si="5"/>
         <v>1976.52</v>
       </c>
-      <c r="AY26" s="103">
+      <c r="AY26" s="96">
         <f t="shared" si="6"/>
         <v>398.19602904073406</v>
       </c>
-      <c r="AZ26" s="103">
+      <c r="AZ26" s="96">
         <f t="shared" si="12"/>
         <v>901.52940875881859</v>
       </c>
-      <c r="BA26" s="103">
+      <c r="BA26" s="96">
         <f t="shared" si="13"/>
         <v>753.72534687285236</v>
       </c>
-      <c r="BB26" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC26" s="105">
+      <c r="BB26" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC26" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD26" s="114">
+      <c r="BD26" s="105">
         <f t="shared" si="15"/>
         <v>21955.44543779955</v>
       </c>
-      <c r="BE26" s="115">
+      <c r="BE26" s="106">
         <f t="shared" si="16"/>
         <v>2021.6800587292405</v>
       </c>
-      <c r="BF26" s="106"/>
-      <c r="BG26" s="116">
+      <c r="BF26" s="99"/>
+      <c r="BG26" s="107">
         <v>2900</v>
       </c>
-      <c r="BH26" s="107">
+      <c r="BH26" s="100">
         <f t="shared" si="7"/>
         <v>31494</v>
       </c>
-      <c r="BI26" s="117">
+      <c r="BI26" s="108">
         <f t="shared" si="17"/>
         <v>9538.5545622004502</v>
       </c>
-      <c r="BJ26" s="108">
+      <c r="BJ26" s="101">
         <f t="shared" si="8"/>
         <v>0.30286894526577918</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62">
       <c r="A27" s="11">
         <f t="shared" si="22"/>
         <v>23</v>
@@ -7135,63 +7158,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT27,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.72</v>
       </c>
-      <c r="AV27" s="102">
+      <c r="AV27" s="95">
         <f t="shared" si="3"/>
         <v>0.74</v>
       </c>
-      <c r="AW27" s="103">
+      <c r="AW27" s="96">
         <f t="shared" si="4"/>
         <v>1272.8</v>
       </c>
-      <c r="AX27" s="104">
+      <c r="AX27" s="97">
         <f t="shared" si="5"/>
         <v>134.68</v>
       </c>
-      <c r="AY27" s="103">
+      <c r="AY27" s="96">
         <f t="shared" si="6"/>
         <v>27.133062752315212</v>
       </c>
-      <c r="AZ27" s="103">
+      <c r="AZ27" s="96">
         <f t="shared" si="12"/>
         <v>61.430180707322819</v>
       </c>
-      <c r="BA27" s="103">
+      <c r="BA27" s="96">
         <f t="shared" si="13"/>
         <v>51.358817374393254</v>
       </c>
-      <c r="BB27" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC27" s="105">
+      <c r="BB27" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC27" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD27" s="114">
+      <c r="BD27" s="105">
         <f t="shared" si="15"/>
         <v>1496.043243459638</v>
       </c>
-      <c r="BE27" s="115">
+      <c r="BE27" s="106">
         <f t="shared" si="16"/>
         <v>2021.6800587292405</v>
       </c>
-      <c r="BF27" s="106"/>
-      <c r="BG27" s="116">
+      <c r="BF27" s="99"/>
+      <c r="BG27" s="107">
         <v>2900</v>
       </c>
-      <c r="BH27" s="107">
+      <c r="BH27" s="100">
         <f t="shared" si="7"/>
         <v>2146</v>
       </c>
-      <c r="BI27" s="117">
+      <c r="BI27" s="108">
         <f t="shared" si="17"/>
         <v>649.95675654036199</v>
       </c>
-      <c r="BJ27" s="108">
+      <c r="BJ27" s="101">
         <f t="shared" si="8"/>
         <v>0.30286894526577912</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62">
       <c r="A28" s="11">
         <f t="shared" si="22"/>
         <v>24</v>
@@ -7327,63 +7350,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT28,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.72</v>
       </c>
-      <c r="AV28" s="102">
+      <c r="AV28" s="95">
         <f t="shared" si="3"/>
         <v>258.74</v>
       </c>
-      <c r="AW28" s="103">
+      <c r="AW28" s="96">
         <f t="shared" si="4"/>
         <v>445032.8</v>
       </c>
-      <c r="AX28" s="104">
+      <c r="AX28" s="97">
         <f t="shared" si="5"/>
         <v>47090.68</v>
       </c>
-      <c r="AY28" s="103">
+      <c r="AY28" s="96">
         <f t="shared" si="6"/>
         <v>9487.0387250459971</v>
       </c>
-      <c r="AZ28" s="103">
+      <c r="AZ28" s="96">
         <f t="shared" si="12"/>
         <v>21478.979670557714</v>
       </c>
-      <c r="BA28" s="103">
+      <c r="BA28" s="96">
         <f t="shared" si="13"/>
         <v>17957.541091149342</v>
       </c>
-      <c r="BB28" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC28" s="105">
+      <c r="BB28" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC28" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD28" s="114">
+      <c r="BD28" s="105">
         <f t="shared" si="15"/>
         <v>523089.49839560367</v>
       </c>
-      <c r="BE28" s="115">
+      <c r="BE28" s="106">
         <f t="shared" si="16"/>
         <v>2021.6800587292403</v>
       </c>
-      <c r="BF28" s="106"/>
-      <c r="BG28" s="116">
+      <c r="BF28" s="99"/>
+      <c r="BG28" s="107">
         <v>2900</v>
       </c>
-      <c r="BH28" s="107">
+      <c r="BH28" s="100">
         <f t="shared" si="7"/>
         <v>750346</v>
       </c>
-      <c r="BI28" s="117">
+      <c r="BI28" s="108">
         <f t="shared" si="17"/>
         <v>227256.50160439633</v>
       </c>
-      <c r="BJ28" s="108">
+      <c r="BJ28" s="101">
         <f t="shared" si="8"/>
         <v>0.30286894526577918</v>
       </c>
     </row>
-    <row r="29" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" ht="15.6" customHeight="1">
       <c r="A29" s="11">
         <f t="shared" si="22"/>
         <v>25</v>
@@ -7465,63 +7488,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT29,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.75</v>
       </c>
-      <c r="AV29" s="102">
+      <c r="AV29" s="95">
         <f t="shared" si="3"/>
         <v>1.96</v>
       </c>
-      <c r="AW29" s="103">
+      <c r="AW29" s="96">
         <f t="shared" si="4"/>
         <v>3429.9999999999995</v>
       </c>
-      <c r="AX29" s="104">
+      <c r="AX29" s="97">
         <f t="shared" si="5"/>
         <v>356.71999999999997</v>
       </c>
-      <c r="AY29" s="103">
+      <c r="AY29" s="96">
         <f t="shared" si="6"/>
         <v>71.865949992618667</v>
       </c>
-      <c r="AZ29" s="103">
+      <c r="AZ29" s="96">
         <f t="shared" si="12"/>
         <v>162.70696511669288</v>
       </c>
-      <c r="BA29" s="103">
+      <c r="BA29" s="96">
         <f t="shared" si="13"/>
         <v>136.03146223487943</v>
       </c>
-      <c r="BB29" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC29" s="105">
+      <c r="BB29" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC29" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD29" s="114">
+      <c r="BD29" s="105">
         <f t="shared" si="15"/>
         <v>4021.2929151093113</v>
       </c>
-      <c r="BE29" s="115">
+      <c r="BE29" s="106">
         <f t="shared" si="16"/>
         <v>2051.6800587292405</v>
       </c>
-      <c r="BF29" s="106"/>
-      <c r="BG29" s="116">
+      <c r="BF29" s="99"/>
+      <c r="BG29" s="107">
         <v>2900</v>
       </c>
-      <c r="BH29" s="107">
+      <c r="BH29" s="100">
         <f t="shared" si="7"/>
         <v>5684</v>
       </c>
-      <c r="BI29" s="117">
+      <c r="BI29" s="108">
         <f t="shared" si="17"/>
         <v>1662.7070848906887</v>
       </c>
-      <c r="BJ29" s="108">
+      <c r="BJ29" s="101">
         <f t="shared" si="8"/>
         <v>0.29252411767957226</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62">
       <c r="A30" s="11">
         <f t="shared" si="22"/>
         <v>26</v>
@@ -7655,63 +7678,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT30,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.75</v>
       </c>
-      <c r="AV30" s="102">
+      <c r="AV30" s="95">
         <f t="shared" si="3"/>
         <v>40.36</v>
       </c>
-      <c r="AW30" s="103">
+      <c r="AW30" s="96">
         <f t="shared" si="4"/>
         <v>70630</v>
       </c>
-      <c r="AX30" s="104">
+      <c r="AX30" s="97">
         <f t="shared" si="5"/>
         <v>7345.5199999999995</v>
       </c>
-      <c r="AY30" s="103">
+      <c r="AY30" s="96">
         <f t="shared" si="6"/>
         <v>1479.8519090316784</v>
       </c>
-      <c r="AZ30" s="103">
+      <c r="AZ30" s="96">
         <f t="shared" si="12"/>
         <v>3350.4352612804714</v>
       </c>
-      <c r="BA30" s="103">
+      <c r="BA30" s="96">
         <f t="shared" si="13"/>
         <v>2801.1376611223131</v>
       </c>
-      <c r="BB30" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC30" s="105">
+      <c r="BB30" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD30" s="114">
+      <c r="BD30" s="105">
         <f t="shared" si="15"/>
         <v>82805.807170312153</v>
       </c>
-      <c r="BE30" s="115">
+      <c r="BE30" s="106">
         <f t="shared" si="16"/>
         <v>2051.6800587292405</v>
       </c>
-      <c r="BF30" s="106"/>
-      <c r="BG30" s="116">
+      <c r="BF30" s="99"/>
+      <c r="BG30" s="107">
         <v>2900</v>
       </c>
-      <c r="BH30" s="107">
+      <c r="BH30" s="100">
         <f t="shared" si="7"/>
         <v>117044</v>
       </c>
-      <c r="BI30" s="117">
+      <c r="BI30" s="108">
         <f t="shared" si="17"/>
         <v>34238.192829687847</v>
       </c>
-      <c r="BJ30" s="108">
+      <c r="BJ30" s="101">
         <f t="shared" si="8"/>
         <v>0.2925241176795722</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62">
       <c r="A31" s="28">
         <f>+A30+1</f>
         <v>27</v>
@@ -7843,63 +7866,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT31,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>2.11</v>
       </c>
-      <c r="AV31" s="102">
+      <c r="AV31" s="95">
         <f t="shared" si="3"/>
         <v>192.12</v>
       </c>
-      <c r="AW31" s="103">
+      <c r="AW31" s="96">
         <f t="shared" si="4"/>
         <v>405373.2</v>
       </c>
-      <c r="AX31" s="104">
+      <c r="AX31" s="97">
         <f t="shared" si="5"/>
         <v>34965.840000000004</v>
       </c>
-      <c r="AY31" s="103">
+      <c r="AY31" s="96">
         <f t="shared" si="6"/>
         <v>7044.3297513172956</v>
       </c>
-      <c r="AZ31" s="103">
+      <c r="AZ31" s="96">
         <f t="shared" si="12"/>
         <v>15948.603131744407</v>
       </c>
-      <c r="BA31" s="103">
+      <c r="BA31" s="96">
         <f t="shared" si="13"/>
         <v>13333.859451308694</v>
       </c>
-      <c r="BB31" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC31" s="105">
+      <c r="BB31" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC31" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD31" s="114">
+      <c r="BD31" s="105">
         <f t="shared" si="15"/>
         <v>463331.97288306174</v>
       </c>
-      <c r="BE31" s="115">
+      <c r="BE31" s="106">
         <f t="shared" si="16"/>
         <v>2411.6800587292405</v>
       </c>
-      <c r="BF31" s="106"/>
-      <c r="BG31" s="116">
+      <c r="BF31" s="99"/>
+      <c r="BG31" s="107">
         <v>4500</v>
       </c>
-      <c r="BH31" s="107">
+      <c r="BH31" s="100">
         <f t="shared" si="7"/>
         <v>864540</v>
       </c>
-      <c r="BI31" s="117">
+      <c r="BI31" s="108">
         <f t="shared" si="17"/>
         <v>401208.02711693826</v>
       </c>
-      <c r="BJ31" s="108">
+      <c r="BJ31" s="101">
         <f t="shared" si="8"/>
         <v>0.46407109806016872</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62">
       <c r="A32" s="28">
         <f t="shared" si="18"/>
         <v>28</v>
@@ -8023,63 +8046,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT32,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>2.11</v>
       </c>
-      <c r="AV32" s="102">
+      <c r="AV32" s="95">
         <f t="shared" si="3"/>
         <v>21.56</v>
       </c>
-      <c r="AW32" s="103">
+      <c r="AW32" s="96">
         <f t="shared" si="4"/>
         <v>45491.599999999991</v>
       </c>
-      <c r="AX32" s="104">
+      <c r="AX32" s="97">
         <f t="shared" si="5"/>
         <v>3923.9199999999996</v>
       </c>
-      <c r="AY32" s="103">
+      <c r="AY32" s="96">
         <f t="shared" si="6"/>
         <v>790.52544991880541</v>
       </c>
-      <c r="AZ32" s="103">
+      <c r="AZ32" s="96">
         <f t="shared" si="12"/>
         <v>1789.7766162836215</v>
       </c>
-      <c r="BA32" s="103">
+      <c r="BA32" s="96">
         <f t="shared" si="13"/>
         <v>1496.3460845836737</v>
       </c>
-      <c r="BB32" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC32" s="105">
+      <c r="BB32" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC32" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD32" s="114">
+      <c r="BD32" s="105">
         <f t="shared" si="15"/>
         <v>51995.822066202418</v>
       </c>
-      <c r="BE32" s="115">
+      <c r="BE32" s="106">
         <f t="shared" si="16"/>
         <v>2411.6800587292405</v>
       </c>
-      <c r="BF32" s="106"/>
-      <c r="BG32" s="116">
+      <c r="BF32" s="99"/>
+      <c r="BG32" s="107">
         <v>4500</v>
       </c>
-      <c r="BH32" s="107">
+      <c r="BH32" s="100">
         <f t="shared" si="7"/>
         <v>97020</v>
       </c>
-      <c r="BI32" s="117">
+      <c r="BI32" s="108">
         <f t="shared" si="17"/>
         <v>45024.177933797582</v>
       </c>
-      <c r="BJ32" s="108">
+      <c r="BJ32" s="101">
         <f t="shared" si="8"/>
         <v>0.46407109806016883</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62">
       <c r="A33" s="28">
         <f>+A31+1</f>
         <v>28</v>
@@ -8161,61 +8184,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT33,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV33" s="102">
+      <c r="AV33" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW33" s="103">
+      <c r="AW33" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX33" s="104">
+      <c r="AX33" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY33" s="103">
+      <c r="AY33" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ33" s="103">
+      <c r="AZ33" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA33" s="103">
+      <c r="BA33" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC33" s="105">
+      <c r="BB33" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC33" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD33" s="114">
+      <c r="BD33" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE33" s="115">
+      <c r="BE33" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF33" s="106"/>
-      <c r="BG33" s="116"/>
-      <c r="BH33" s="107">
+      <c r="BF33" s="99"/>
+      <c r="BG33" s="107"/>
+      <c r="BH33" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="117">
+      <c r="BI33" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ33" s="108">
+      <c r="BJ33" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62">
       <c r="A34" s="28"/>
       <c r="B34" s="31">
         <v>10007050</v>
@@ -8331,63 +8354,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT34,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.31</v>
       </c>
-      <c r="AV34" s="102">
+      <c r="AV34" s="95">
         <f t="shared" si="3"/>
         <v>49.1</v>
       </c>
-      <c r="AW34" s="103">
+      <c r="AW34" s="96">
         <f t="shared" si="4"/>
         <v>64321</v>
       </c>
-      <c r="AX34" s="104">
+      <c r="AX34" s="97">
         <f t="shared" si="5"/>
         <v>8936.2000000000007</v>
       </c>
-      <c r="AY34" s="103">
+      <c r="AY34" s="96">
         <f t="shared" si="6"/>
         <v>1800.3153799171312</v>
       </c>
-      <c r="AZ34" s="103">
+      <c r="AZ34" s="96">
         <f t="shared" si="12"/>
         <v>4075.9755036885817</v>
       </c>
-      <c r="BA34" s="103">
+      <c r="BA34" s="96">
         <f t="shared" si="13"/>
         <v>3407.7269365982552</v>
       </c>
-      <c r="BB34" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC34" s="105">
+      <c r="BB34" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC34" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD34" s="114">
+      <c r="BD34" s="105">
         <f t="shared" si="15"/>
         <v>79133.4908836057</v>
       </c>
-      <c r="BE34" s="115">
+      <c r="BE34" s="106">
         <f t="shared" si="16"/>
         <v>1611.6800587292403</v>
       </c>
-      <c r="BF34" s="106"/>
-      <c r="BG34" s="116">
+      <c r="BF34" s="99"/>
+      <c r="BG34" s="107">
         <v>4500</v>
       </c>
-      <c r="BH34" s="107">
+      <c r="BH34" s="100">
         <f t="shared" si="7"/>
         <v>220950</v>
       </c>
-      <c r="BI34" s="117">
+      <c r="BI34" s="108">
         <f t="shared" si="17"/>
         <v>141816.5091163943</v>
       </c>
-      <c r="BJ34" s="108">
+      <c r="BJ34" s="101">
         <f t="shared" si="8"/>
         <v>0.64184887583794659</v>
       </c>
     </row>
-    <row r="35" spans="1:62" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" ht="18.600000000000001" customHeight="1">
       <c r="A35" s="28">
         <f>+A32+1</f>
         <v>29</v>
@@ -8471,61 +8494,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT35,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV35" s="102">
+      <c r="AV35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW35" s="103">
+      <c r="AW35" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX35" s="104">
+      <c r="AX35" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY35" s="103">
+      <c r="AY35" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ35" s="103">
+      <c r="AZ35" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA35" s="103">
+      <c r="BA35" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB35" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC35" s="105">
+      <c r="BB35" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC35" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD35" s="114">
+      <c r="BD35" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="115">
+      <c r="BE35" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF35" s="106"/>
-      <c r="BG35" s="116"/>
-      <c r="BH35" s="107">
+      <c r="BF35" s="99"/>
+      <c r="BG35" s="107"/>
+      <c r="BH35" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI35" s="117">
+      <c r="BI35" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ35" s="108">
+      <c r="BJ35" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:62" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" ht="18.600000000000001" customHeight="1">
       <c r="A36" s="28">
         <f>+A33+1</f>
         <v>29</v>
@@ -8606,61 +8629,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT36,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV36" s="102">
+      <c r="AV36" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW36" s="103">
+      <c r="AW36" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX36" s="104">
+      <c r="AX36" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY36" s="103">
+      <c r="AY36" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ36" s="103">
+      <c r="AZ36" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA36" s="103">
+      <c r="BA36" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB36" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC36" s="105">
+      <c r="BB36" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC36" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD36" s="114">
+      <c r="BD36" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE36" s="115">
+      <c r="BE36" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF36" s="106"/>
-      <c r="BG36" s="116"/>
-      <c r="BH36" s="107">
+      <c r="BF36" s="99"/>
+      <c r="BG36" s="107"/>
+      <c r="BH36" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI36" s="117">
+      <c r="BI36" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ36" s="108">
+      <c r="BJ36" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62">
       <c r="A37" s="28">
         <f t="shared" ref="A37:A38" si="24">+A35+1</f>
         <v>30</v>
@@ -8741,61 +8764,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT37,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV37" s="102">
+      <c r="AV37" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW37" s="103">
+      <c r="AW37" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX37" s="104">
+      <c r="AX37" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY37" s="103">
+      <c r="AY37" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ37" s="103">
+      <c r="AZ37" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA37" s="103">
+      <c r="BA37" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB37" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC37" s="105">
+      <c r="BB37" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC37" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD37" s="114">
+      <c r="BD37" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE37" s="115">
+      <c r="BE37" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF37" s="106"/>
-      <c r="BG37" s="116"/>
-      <c r="BH37" s="107">
+      <c r="BF37" s="99"/>
+      <c r="BG37" s="107"/>
+      <c r="BH37" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI37" s="117">
+      <c r="BI37" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ37" s="108">
+      <c r="BJ37" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62">
       <c r="A38" s="28">
         <f t="shared" si="24"/>
         <v>30</v>
@@ -8876,61 +8899,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT38,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV38" s="102">
+      <c r="AV38" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW38" s="103">
+      <c r="AW38" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX38" s="104">
+      <c r="AX38" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY38" s="103">
+      <c r="AY38" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ38" s="103">
+      <c r="AZ38" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA38" s="103">
+      <c r="BA38" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB38" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC38" s="105">
+      <c r="BB38" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC38" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD38" s="114">
+      <c r="BD38" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE38" s="115">
+      <c r="BE38" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF38" s="106"/>
-      <c r="BG38" s="116"/>
-      <c r="BH38" s="107">
+      <c r="BF38" s="99"/>
+      <c r="BG38" s="107"/>
+      <c r="BH38" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI38" s="117">
+      <c r="BI38" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ38" s="108">
+      <c r="BJ38" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" s="15" customFormat="1">
       <c r="A39" s="23">
         <f>+A38+1</f>
         <v>31</v>
@@ -9058,63 +9081,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT39,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.53</v>
       </c>
-      <c r="AV39" s="102">
+      <c r="AV39" s="95">
         <f t="shared" si="3"/>
         <v>21.21</v>
       </c>
-      <c r="AW39" s="103">
+      <c r="AW39" s="96">
         <f t="shared" si="4"/>
         <v>32451.300000000003</v>
       </c>
-      <c r="AX39" s="104">
+      <c r="AX39" s="97">
         <f t="shared" si="5"/>
         <v>3860.2200000000003</v>
       </c>
-      <c r="AY39" s="110">
+      <c r="AY39" s="103">
         <f t="shared" si="6"/>
         <v>777.6922445629807</v>
       </c>
-      <c r="AZ39" s="103">
+      <c r="AZ39" s="96">
         <f t="shared" si="12"/>
         <v>1760.7218010842123</v>
       </c>
-      <c r="BA39" s="103">
+      <c r="BA39" s="96">
         <f t="shared" si="13"/>
         <v>1472.054752041731</v>
       </c>
-      <c r="BB39" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC39" s="105">
+      <c r="BB39" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC39" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD39" s="114">
+      <c r="BD39" s="105">
         <f t="shared" si="15"/>
         <v>38849.934045647198</v>
       </c>
-      <c r="BE39" s="115">
+      <c r="BE39" s="106">
         <f t="shared" si="16"/>
         <v>1831.6800587292407</v>
       </c>
-      <c r="BF39" s="106"/>
-      <c r="BG39" s="116">
+      <c r="BF39" s="99"/>
+      <c r="BG39" s="107">
         <v>2500</v>
       </c>
-      <c r="BH39" s="107">
+      <c r="BH39" s="100">
         <f t="shared" si="7"/>
         <v>53025</v>
       </c>
-      <c r="BI39" s="117">
+      <c r="BI39" s="108">
         <f t="shared" si="17"/>
         <v>14175.065954352802</v>
       </c>
-      <c r="BJ39" s="108">
+      <c r="BJ39" s="101">
         <f t="shared" si="8"/>
         <v>0.26732797650830364</v>
       </c>
     </row>
-    <row r="40" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:62" s="15" customFormat="1">
       <c r="A40" s="23">
         <f t="shared" ref="A40" si="25">+A39+1</f>
         <v>32</v>
@@ -9235,63 +9258,63 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT40,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>1.53</v>
       </c>
-      <c r="AV40" s="102">
+      <c r="AV40" s="95">
         <f t="shared" si="3"/>
         <v>39.36</v>
       </c>
-      <c r="AW40" s="103">
+      <c r="AW40" s="96">
         <f t="shared" si="4"/>
         <v>60220.799999999996</v>
       </c>
-      <c r="AX40" s="104">
+      <c r="AX40" s="97">
         <f t="shared" si="5"/>
         <v>7163.5199999999995</v>
       </c>
-      <c r="AY40" s="110">
+      <c r="AY40" s="103">
         <f t="shared" si="6"/>
         <v>1443.1856080150362</v>
       </c>
-      <c r="AZ40" s="103">
+      <c r="AZ40" s="96">
         <f t="shared" si="12"/>
         <v>3267.4215035678731</v>
       </c>
-      <c r="BA40" s="103">
+      <c r="BA40" s="96">
         <f t="shared" si="13"/>
         <v>2731.7338538596196</v>
       </c>
-      <c r="BB40" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC40" s="105">
+      <c r="BB40" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC40" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD40" s="114">
+      <c r="BD40" s="105">
         <f t="shared" si="15"/>
         <v>72094.927111582903</v>
       </c>
-      <c r="BE40" s="115">
+      <c r="BE40" s="106">
         <f t="shared" si="16"/>
         <v>1831.6800587292405</v>
       </c>
-      <c r="BF40" s="106"/>
-      <c r="BG40" s="116">
+      <c r="BF40" s="99"/>
+      <c r="BG40" s="107">
         <v>2500</v>
       </c>
-      <c r="BH40" s="107">
+      <c r="BH40" s="100">
         <f t="shared" si="7"/>
         <v>98400</v>
       </c>
-      <c r="BI40" s="117">
+      <c r="BI40" s="108">
         <f t="shared" si="17"/>
         <v>26305.072888417097</v>
       </c>
-      <c r="BJ40" s="108">
+      <c r="BJ40" s="101">
         <f t="shared" si="8"/>
         <v>0.26732797650830381</v>
       </c>
     </row>
-    <row r="41" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:62" s="15" customFormat="1">
       <c r="A41" s="23"/>
       <c r="B41" s="32"/>
       <c r="C41" s="32" t="s">
@@ -9362,61 +9385,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT41,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV41" s="102">
+      <c r="AV41" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW41" s="103">
+      <c r="AW41" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX41" s="104">
+      <c r="AX41" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY41" s="110">
+      <c r="AY41" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ41" s="103">
+      <c r="AZ41" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA41" s="103">
+      <c r="BA41" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB41" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC41" s="105">
+      <c r="BB41" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC41" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD41" s="114">
+      <c r="BD41" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE41" s="115">
+      <c r="BE41" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF41" s="106"/>
-      <c r="BG41" s="116"/>
-      <c r="BH41" s="107">
+      <c r="BF41" s="99"/>
+      <c r="BG41" s="107"/>
+      <c r="BH41" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI41" s="117">
+      <c r="BI41" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ41" s="108">
+      <c r="BJ41" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:62" s="15" customFormat="1">
       <c r="A42" s="23"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32" t="s">
@@ -9488,61 +9511,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT42,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV42" s="102">
+      <c r="AV42" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW42" s="103">
+      <c r="AW42" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX42" s="104">
+      <c r="AX42" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY42" s="110">
+      <c r="AY42" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ42" s="103">
+      <c r="AZ42" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA42" s="103">
+      <c r="BA42" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB42" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC42" s="105">
+      <c r="BB42" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC42" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD42" s="114">
+      <c r="BD42" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE42" s="115">
+      <c r="BE42" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF42" s="106"/>
-      <c r="BG42" s="116"/>
-      <c r="BH42" s="107">
+      <c r="BF42" s="99"/>
+      <c r="BG42" s="107"/>
+      <c r="BH42" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI42" s="117">
+      <c r="BI42" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ42" s="108">
+      <c r="BJ42" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:62" s="15" customFormat="1">
       <c r="A43" s="48">
         <f>+A40+1</f>
         <v>33</v>
@@ -9623,61 +9646,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT43,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV43" s="102">
+      <c r="AV43" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW43" s="103">
+      <c r="AW43" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX43" s="104">
+      <c r="AX43" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY43" s="110">
+      <c r="AY43" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ43" s="103">
+      <c r="AZ43" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA43" s="103">
+      <c r="BA43" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB43" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC43" s="105">
+      <c r="BB43" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC43" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD43" s="114">
+      <c r="BD43" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="115">
+      <c r="BE43" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF43" s="106"/>
-      <c r="BG43" s="116"/>
-      <c r="BH43" s="107">
+      <c r="BF43" s="99"/>
+      <c r="BG43" s="107"/>
+      <c r="BH43" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI43" s="117">
+      <c r="BI43" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ43" s="108">
+      <c r="BJ43" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:62" s="15" customFormat="1">
       <c r="A44" s="48">
         <f t="shared" ref="A44:A45" si="29">+A43+1</f>
         <v>34</v>
@@ -9758,61 +9781,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT44,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV44" s="102">
+      <c r="AV44" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW44" s="103">
+      <c r="AW44" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX44" s="104">
+      <c r="AX44" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY44" s="110">
+      <c r="AY44" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ44" s="103">
+      <c r="AZ44" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA44" s="103">
+      <c r="BA44" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB44" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC44" s="105">
+      <c r="BB44" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC44" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD44" s="114">
+      <c r="BD44" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE44" s="115">
+      <c r="BE44" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF44" s="106"/>
-      <c r="BG44" s="116"/>
-      <c r="BH44" s="107">
+      <c r="BF44" s="99"/>
+      <c r="BG44" s="107"/>
+      <c r="BH44" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI44" s="117">
+      <c r="BI44" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ44" s="108">
+      <c r="BJ44" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:62" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:62" s="15" customFormat="1">
       <c r="A45" s="48">
         <f t="shared" si="29"/>
         <v>35</v>
@@ -9889,61 +9912,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT45,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV45" s="102">
+      <c r="AV45" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW45" s="103">
+      <c r="AW45" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX45" s="104">
+      <c r="AX45" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY45" s="110">
+      <c r="AY45" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ45" s="103">
+      <c r="AZ45" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA45" s="103">
+      <c r="BA45" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB45" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC45" s="105">
+      <c r="BB45" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC45" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD45" s="114">
+      <c r="BD45" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="115">
+      <c r="BE45" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF45" s="106"/>
-      <c r="BG45" s="116"/>
-      <c r="BH45" s="107">
+      <c r="BF45" s="99"/>
+      <c r="BG45" s="107"/>
+      <c r="BH45" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI45" s="117">
+      <c r="BI45" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ45" s="108">
+      <c r="BJ45" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62">
       <c r="A46" s="43">
         <f>+A45+1</f>
         <v>36</v>
@@ -10025,61 +10048,61 @@
         <f>INDEX('[1]Detalle Costos'!$L$5:$L$158,MATCH(AT46,'[1]Detalle Costos'!$C$5:$C$158,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="AV46" s="102">
+      <c r="AV46" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW46" s="103">
+      <c r="AW46" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AX46" s="104">
+      <c r="AX46" s="97">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY46" s="103">
+      <c r="AY46" s="96">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AZ46" s="103">
+      <c r="AZ46" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA46" s="103">
+      <c r="BA46" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="BB46" s="103">
-        <v>0</v>
-      </c>
-      <c r="BC46" s="105">
+      <c r="BB46" s="96">
+        <v>0</v>
+      </c>
+      <c r="BC46" s="98">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="BD46" s="114">
+      <c r="BD46" s="105">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BE46" s="115">
+      <c r="BE46" s="106">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BF46" s="106"/>
-      <c r="BG46" s="116"/>
-      <c r="BH46" s="107">
+      <c r="BF46" s="99"/>
+      <c r="BG46" s="107"/>
+      <c r="BH46" s="100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="BI46" s="117">
+      <c r="BI46" s="108">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="BJ46" s="108">
+      <c r="BJ46" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:62" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:62" ht="3.6" customHeight="1" thickBot="1">
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -10112,26 +10135,19 @@
       <c r="AG47" s="5"/>
       <c r="AH47" s="27"/>
       <c r="AO47" s="77"/>
-      <c r="AV47" s="111"/>
-      <c r="AW47" s="112"/>
-      <c r="AX47" s="112"/>
-      <c r="AY47" s="112"/>
-      <c r="AZ47" s="112"/>
-      <c r="BA47" s="112"/>
-      <c r="BB47" s="112"/>
-      <c r="BC47" s="112"/>
-      <c r="BD47" s="114"/>
-      <c r="BE47" s="114"/>
-      <c r="BF47" s="113"/>
-      <c r="BG47" s="117"/>
-      <c r="BH47" s="107"/>
-      <c r="BI47" s="117"/>
-      <c r="BJ47" s="108">
+      <c r="AV47" s="104"/>
+      <c r="BD47" s="105"/>
+      <c r="BE47" s="105"/>
+      <c r="BF47" s="97"/>
+      <c r="BG47" s="108"/>
+      <c r="BH47" s="100"/>
+      <c r="BI47" s="108"/>
+      <c r="BJ47" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:62" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:62" ht="16.5" thickBot="1">
       <c r="C48" s="1" t="s">
         <v>93</v>
       </c>
@@ -10233,65 +10249,65 @@
         <v>113</v>
       </c>
       <c r="AU48" s="15"/>
-      <c r="AV48" s="118">
+      <c r="AV48" s="109">
         <f>SUBTOTAL(9,AV3:AV46)</f>
         <v>1787.0299999999995</v>
       </c>
-      <c r="AW48" s="119">
+      <c r="AW48" s="110">
         <f>SUBTOTAL(9,AW3:AW46)</f>
         <v>3120153.7</v>
       </c>
-      <c r="AX48" s="119">
+      <c r="AX48" s="110">
         <f>SUBTOTAL(9,AX3:AX46)</f>
         <v>325239.45999999996</v>
       </c>
-      <c r="AY48" s="119">
+      <c r="AY48" s="110">
         <v>65523.779905770061</v>
       </c>
-      <c r="AZ48" s="119">
+      <c r="AZ48" s="110">
         <v>148348.0754451447</v>
       </c>
-      <c r="BA48" s="119">
+      <c r="BA48" s="110">
         <v>124026.6856926513</v>
       </c>
-      <c r="BB48" s="119">
+      <c r="BB48" s="110">
         <f>SUBTOTAL(9,BB3:BB46)</f>
         <v>0</v>
       </c>
-      <c r="BC48" s="120">
-        <v>0</v>
-      </c>
-      <c r="BD48" s="121">
+      <c r="BC48" s="111">
+        <v>0</v>
+      </c>
+      <c r="BD48" s="112">
         <f>SUBTOTAL(9,BD3:BD46)</f>
         <v>3659265.0153509141</v>
       </c>
-      <c r="BE48" s="121">
+      <c r="BE48" s="112">
         <f>BD48/$AV$48</f>
         <v>2047.6796782096076</v>
       </c>
-      <c r="BF48" s="122"/>
-      <c r="BG48" s="123">
+      <c r="BF48" s="113"/>
+      <c r="BG48" s="114">
         <f>BH48/$AV$48</f>
         <v>2640.9802857254781</v>
       </c>
-      <c r="BH48" s="124">
+      <c r="BH48" s="115">
         <f>SUBTOTAL(9,BH3:BH46)</f>
         <v>4719511</v>
       </c>
-      <c r="BI48" s="123">
+      <c r="BI48" s="114">
         <f>SUBTOTAL(9,BI3:BI46)</f>
         <v>1060245.9846490852</v>
       </c>
-      <c r="BJ48" s="125">
+      <c r="BJ48" s="116">
         <f t="shared" si="8"/>
         <v>0.22465166087102778</v>
       </c>
     </row>
-    <row r="49" spans="4:41" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:41" ht="3.6" customHeight="1">
       <c r="AH49" s="27"/>
       <c r="AJ49" s="5"/>
     </row>
-    <row r="50" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:41">
       <c r="D50" s="74"/>
       <c r="AJ50" s="5"/>
       <c r="AL50" s="5"/>
@@ -10300,17 +10316,17 @@
         <v>1728695</v>
       </c>
     </row>
-    <row r="51" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:41">
       <c r="D51" s="5"/>
       <c r="E51" s="5">
         <f>+E48+F48</f>
         <v>167135</v>
       </c>
-      <c r="AD51" s="96" t="s">
+      <c r="AD51" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="AE51" s="97"/>
-      <c r="AF51" s="97"/>
+      <c r="AE51" s="128"/>
+      <c r="AF51" s="128"/>
       <c r="AG51" s="62">
         <f>ROUND(+AG48/1000,0)</f>
         <v>1878</v>
@@ -10328,7 +10344,7 @@
         <v>642.57680000000005</v>
       </c>
     </row>
-    <row r="52" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:41">
       <c r="AD52" s="3" t="s">
         <v>70</v>
       </c>
@@ -10355,7 +10371,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:41">
       <c r="E53" s="3">
         <v>115</v>
       </c>
@@ -10381,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:41">
       <c r="E54" s="3">
         <v>167</v>
       </c>
@@ -10402,16 +10418,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:41">
       <c r="E55" s="3">
         <f>+E54-E53</f>
         <v>52</v>
       </c>
-      <c r="AD55" s="96" t="s">
+      <c r="AD55" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="AE55" s="97"/>
-      <c r="AF55" s="97"/>
+      <c r="AE55" s="128"/>
+      <c r="AF55" s="128"/>
       <c r="AG55" s="64">
         <f>+AG51-AG52-AG53-AG54</f>
         <v>1554</v>
@@ -10425,21 +10441,24 @@
         <v>593.57680000000005</v>
       </c>
     </row>
-    <row r="56" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:41">
+      <c r="AG56" s="3">
+        <v>0</v>
+      </c>
       <c r="AJ56" s="63"/>
       <c r="AK56" s="63"/>
     </row>
-    <row r="57" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:41">
       <c r="AK57" s="63"/>
     </row>
-    <row r="58" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:41">
       <c r="AE58" s="5"/>
     </row>
-    <row r="59" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:41">
       <c r="AE59" s="5"/>
       <c r="AG59" s="63"/>
     </row>
-    <row r="61" spans="4:41" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:41">
       <c r="AG61" s="63"/>
     </row>
   </sheetData>
@@ -10465,91 +10484,92 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BJ59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="39.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="39.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="3" customWidth="1"/>
     <col min="6" max="30" width="12" style="3" customWidth="1"/>
-    <col min="31" max="31" width="12.21875" style="3" customWidth="1"/>
-    <col min="32" max="32" width="1.109375" style="3" customWidth="1"/>
-    <col min="33" max="34" width="11.6640625" style="3" customWidth="1"/>
-    <col min="35" max="35" width="11.88671875" style="3" customWidth="1"/>
-    <col min="36" max="36" width="12.6640625" style="3" customWidth="1"/>
-    <col min="37" max="37" width="0.88671875" style="8" customWidth="1"/>
-    <col min="38" max="38" width="11.5546875" style="3" customWidth="1"/>
-    <col min="39" max="39" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="9.77734375" style="86" customWidth="1"/>
-    <col min="45" max="45" width="9.77734375" style="76" customWidth="1"/>
-    <col min="47" max="51" width="9.77734375" style="3" customWidth="1"/>
-    <col min="52" max="16384" width="11.5546875" style="3"/>
+    <col min="31" max="31" width="12.25" style="3" customWidth="1"/>
+    <col min="32" max="32" width="1.125" style="3" customWidth="1"/>
+    <col min="33" max="34" width="11.625" style="3" customWidth="1"/>
+    <col min="35" max="35" width="11.875" style="3" customWidth="1"/>
+    <col min="36" max="36" width="12.625" style="3" customWidth="1"/>
+    <col min="37" max="37" width="0.875" style="8" customWidth="1"/>
+    <col min="38" max="38" width="11.5" style="3" customWidth="1"/>
+    <col min="39" max="39" width="12.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="9.75" style="86" customWidth="1"/>
+    <col min="45" max="45" width="9.75" style="76" customWidth="1"/>
+    <col min="46" max="46" width="11"/>
+    <col min="47" max="51" width="9.75" style="3" customWidth="1"/>
+    <col min="52" max="16384" width="11.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:62">
+      <c r="A1" s="129" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="98" t="s">
+      <c r="C1" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="98"/>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="98"/>
-      <c r="AG1" s="98" t="s">
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="129"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AG1" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="98"/>
-      <c r="AI1" s="98"/>
-      <c r="AJ1" s="98"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="129"/>
       <c r="AK1" s="27"/>
       <c r="AL1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AM1" s="94" t="s">
+      <c r="AM1" s="125" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A2" s="98"/>
+    <row r="2" spans="1:62">
+      <c r="A2" s="129"/>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="98"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
@@ -10649,7 +10669,7 @@
       <c r="AL2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="AM2" s="95"/>
+      <c r="AM2" s="126"/>
       <c r="AN2" s="65" t="s">
         <v>75</v>
       </c>
@@ -10660,7 +10680,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -10736,7 +10756,7 @@
       </c>
       <c r="BJ3" s="5"/>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62">
       <c r="A4" s="17">
         <f>+A3+1</f>
         <v>2</v>
@@ -10861,7 +10881,7 @@
       </c>
       <c r="BG4" s="15"/>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62">
       <c r="A5" s="17">
         <f t="shared" ref="A5:A32" si="5">+A4+1</f>
         <v>3</v>
@@ -10934,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62">
       <c r="A6" s="17">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -11007,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62">
       <c r="A7" s="17">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -11143,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62">
       <c r="A8" s="17">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -11216,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62">
       <c r="A9" s="17">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -11299,7 +11319,7 @@
       <c r="AR9" s="87"/>
       <c r="AS9" s="77"/>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62">
       <c r="A10" s="17"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39" t="s">
@@ -11366,7 +11386,7 @@
       <c r="AR10" s="87"/>
       <c r="AS10" s="77"/>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62">
       <c r="A11" s="17"/>
       <c r="B11" s="39"/>
       <c r="C11" s="39" t="s">
@@ -11443,7 +11463,7 @@
       <c r="AR11" s="87"/>
       <c r="AS11" s="77"/>
     </row>
-    <row r="12" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" s="8" customFormat="1">
       <c r="A12" s="37">
         <v>8</v>
       </c>
@@ -11563,7 +11583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" s="8" customFormat="1">
       <c r="A13" s="37">
         <f>+A12+1</f>
         <v>9</v>
@@ -11692,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62">
       <c r="A14" s="7">
         <f>+A13+1</f>
         <v>10</v>
@@ -11765,7 +11785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62">
       <c r="A15" s="7">
         <f t="shared" ref="A15:A17" si="9">+A14+1</f>
         <v>11</v>
@@ -11838,7 +11858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62">
       <c r="A16" s="7">
         <f t="shared" si="9"/>
         <v>12</v>
@@ -11976,7 +11996,7 @@
       </c>
       <c r="BH16" s="15"/>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:61">
       <c r="A17" s="7">
         <f t="shared" si="9"/>
         <v>13</v>
@@ -12110,7 +12130,7 @@
       </c>
       <c r="BG17" s="8"/>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:61">
       <c r="A18" s="23">
         <f>+A17+1</f>
         <v>14</v>
@@ -12183,7 +12203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:61">
       <c r="A19" s="23">
         <f t="shared" ref="A19:A23" si="10">+A18+1</f>
         <v>15</v>
@@ -12256,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:61">
       <c r="A20" s="23">
         <f t="shared" si="10"/>
         <v>16</v>
@@ -12394,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:61">
       <c r="A21" s="23">
         <f t="shared" si="10"/>
         <v>17</v>
@@ -12514,7 +12534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:61">
       <c r="A22" s="23">
         <f t="shared" si="10"/>
         <v>18</v>
@@ -12642,7 +12662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:61">
       <c r="A23" s="23">
         <f t="shared" si="10"/>
         <v>19</v>
@@ -12758,7 +12778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:61" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:61" s="8" customFormat="1">
       <c r="A24" s="11">
         <f>+A23+1</f>
         <v>20</v>
@@ -12888,7 +12908,7 @@
       <c r="BH24" s="3"/>
       <c r="BI24" s="3"/>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:61">
       <c r="A25" s="11">
         <f t="shared" ref="A25:A30" si="11">+A24+1</f>
         <v>21</v>
@@ -12962,7 +12982,7 @@
       </c>
       <c r="BA25" s="8"/>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:61">
       <c r="A26" s="11">
         <f t="shared" si="11"/>
         <v>22</v>
@@ -13083,7 +13103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:61">
       <c r="A27" s="11">
         <f t="shared" si="11"/>
         <v>23</v>
@@ -13156,7 +13176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:61">
       <c r="A28" s="11">
         <f t="shared" si="11"/>
         <v>24</v>
@@ -13296,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:61" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:61" ht="15.6" customHeight="1">
       <c r="A29" s="11">
         <f t="shared" si="11"/>
         <v>25</v>
@@ -13369,7 +13389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:61">
       <c r="A30" s="11">
         <f t="shared" si="11"/>
         <v>26</v>
@@ -13504,7 +13524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:61">
       <c r="A31" s="28">
         <f>+A30+1</f>
         <v>27</v>
@@ -13629,7 +13649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:61">
       <c r="A32" s="28">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -13736,7 +13756,7 @@
       </c>
       <c r="BH32" s="5"/>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:61">
       <c r="A33" s="28">
         <f>+A31+1</f>
         <v>28</v>
@@ -13810,7 +13830,7 @@
       </c>
       <c r="BH33" s="5"/>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:61">
       <c r="A34" s="28"/>
       <c r="B34" s="31">
         <v>10007050</v>
@@ -13922,7 +13942,7 @@
       <c r="AS34" s="77"/>
       <c r="BH34" s="5"/>
     </row>
-    <row r="35" spans="1:61" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:61" ht="18.600000000000001" customHeight="1">
       <c r="A35" s="28">
         <f>+A32+1</f>
         <v>29</v>
@@ -14001,7 +14021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:61" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:61" ht="18.600000000000001" customHeight="1">
       <c r="A36" s="28">
         <f>+A33+1</f>
         <v>29</v>
@@ -14084,7 +14104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:61">
       <c r="A37" s="28">
         <f t="shared" ref="A37:A38" si="12">+A35+1</f>
         <v>30</v>
@@ -14161,7 +14181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:61">
       <c r="A38" s="28">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -14238,7 +14258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:61" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:61" s="15" customFormat="1">
       <c r="A39" s="23">
         <f>+A38+1</f>
         <v>31</v>
@@ -14355,7 +14375,7 @@
       <c r="BH39" s="3"/>
       <c r="BI39" s="3"/>
     </row>
-    <row r="40" spans="1:61" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:61" s="15" customFormat="1">
       <c r="A40" s="23">
         <f t="shared" ref="A40" si="13">+A39+1</f>
         <v>32</v>
@@ -14467,7 +14487,7 @@
       <c r="BH40" s="3"/>
       <c r="BI40" s="3"/>
     </row>
-    <row r="41" spans="1:61" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:61" s="15" customFormat="1">
       <c r="A41" s="48">
         <f>+A40+1</f>
         <v>33</v>
@@ -14543,7 +14563,7 @@
       <c r="BH41" s="3"/>
       <c r="BI41" s="3"/>
     </row>
-    <row r="42" spans="1:61" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:61" s="15" customFormat="1">
       <c r="A42" s="48">
         <f t="shared" ref="A42:A43" si="14">+A41+1</f>
         <v>34</v>
@@ -14619,7 +14639,7 @@
       <c r="BH42" s="3"/>
       <c r="BI42" s="3"/>
     </row>
-    <row r="43" spans="1:61" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:61" s="15" customFormat="1">
       <c r="A43" s="48">
         <f t="shared" si="14"/>
         <v>35</v>
@@ -14693,7 +14713,7 @@
       <c r="BH43" s="3"/>
       <c r="BI43" s="3"/>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:61">
       <c r="A44" s="43">
         <f>+A43+1</f>
         <v>36</v>
@@ -14766,7 +14786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:61" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:61" ht="3.6" customHeight="1">
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -14810,7 +14830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:61" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:61" ht="15.75">
       <c r="C46" s="1" t="s">
         <v>94</v>
       </c>
@@ -14981,21 +15001,21 @@
         <v>-2165902.7999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:61" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:61" ht="3.6" customHeight="1">
       <c r="AK47" s="27"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:61">
       <c r="D48" s="74"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:44">
       <c r="D49" s="5"/>
-      <c r="AG49" s="96" t="s">
+      <c r="AG49" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="AH49" s="97"/>
-      <c r="AI49" s="97"/>
+      <c r="AH49" s="128"/>
+      <c r="AI49" s="128"/>
       <c r="AJ49" s="62">
         <f>+AJ46/1000</f>
         <v>2165.9027999999998</v>
@@ -15011,7 +15031,7 @@
       </c>
       <c r="AR49" s="88"/>
     </row>
-    <row r="50" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:44">
       <c r="AG50" s="3" t="s">
         <v>70</v>
       </c>
@@ -15039,7 +15059,7 @@
       </c>
       <c r="AR50" s="88"/>
     </row>
-    <row r="51" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:44">
       <c r="AH51" s="61"/>
       <c r="AI51" s="61"/>
       <c r="AJ51" s="63">
@@ -15054,7 +15074,7 @@
       </c>
       <c r="AR51" s="88"/>
     </row>
-    <row r="52" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:44">
       <c r="AH52" s="61"/>
       <c r="AI52" s="61"/>
       <c r="AJ52" s="63">
@@ -15069,12 +15089,12 @@
       </c>
       <c r="AR52" s="88"/>
     </row>
-    <row r="53" spans="4:44" x14ac:dyDescent="0.3">
-      <c r="AG53" s="96" t="s">
+    <row r="53" spans="4:44">
+      <c r="AG53" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="AH53" s="97"/>
-      <c r="AI53" s="97"/>
+      <c r="AH53" s="128"/>
+      <c r="AI53" s="128"/>
       <c r="AJ53" s="64">
         <f>+AJ49-AJ50-AJ51-AJ52</f>
         <v>2165.9027999999998</v>
@@ -15086,21 +15106,21 @@
       </c>
       <c r="AR53" s="88"/>
     </row>
-    <row r="54" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:44">
       <c r="AM54" s="63"/>
       <c r="AN54" s="63"/>
     </row>
-    <row r="55" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:44">
       <c r="AN55" s="63"/>
     </row>
-    <row r="56" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:44">
       <c r="AH56" s="5"/>
     </row>
-    <row r="57" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:44">
       <c r="AH57" s="5"/>
       <c r="AJ57" s="63"/>
     </row>
-    <row r="59" spans="4:44" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:44">
       <c r="AJ59" s="63"/>
     </row>
   </sheetData>
@@ -15126,80 +15146,80 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AW56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="3" customWidth="1"/>
     <col min="6" max="21" width="12" style="3" customWidth="1"/>
-    <col min="22" max="22" width="12.21875" style="3" customWidth="1"/>
-    <col min="23" max="23" width="1.109375" style="3" customWidth="1"/>
-    <col min="24" max="25" width="11.6640625" style="3" customWidth="1"/>
-    <col min="26" max="26" width="11.88671875" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.6640625" style="3" customWidth="1"/>
-    <col min="28" max="28" width="0.88671875" style="8" customWidth="1"/>
-    <col min="29" max="29" width="11.5546875" style="3" customWidth="1"/>
-    <col min="30" max="30" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.77734375" style="3" customWidth="1"/>
-    <col min="33" max="33" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="34" max="38" width="9.77734375" style="3" customWidth="1"/>
-    <col min="39" max="16384" width="11.5546875" style="3"/>
+    <col min="22" max="22" width="12.25" style="3" customWidth="1"/>
+    <col min="23" max="23" width="1.125" style="3" customWidth="1"/>
+    <col min="24" max="25" width="11.625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="11.875" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.625" style="3" customWidth="1"/>
+    <col min="28" max="28" width="0.875" style="8" customWidth="1"/>
+    <col min="29" max="29" width="11.5" style="3" customWidth="1"/>
+    <col min="30" max="30" width="12.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.75" style="3" customWidth="1"/>
+    <col min="33" max="33" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="38" width="9.75" style="3" customWidth="1"/>
+    <col min="39" max="16384" width="11.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:49">
+      <c r="A1" s="129" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="98" t="s">
+      <c r="C1" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="X1" s="98" t="s">
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="X1" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="129"/>
       <c r="AB1" s="27"/>
       <c r="AC1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="94" t="s">
+      <c r="AD1" s="125" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A2" s="98"/>
+    <row r="2" spans="1:49">
+      <c r="A2" s="129"/>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="98"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
@@ -15274,7 +15294,7 @@
       <c r="AC2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="AD2" s="95"/>
+      <c r="AD2" s="126"/>
       <c r="AE2" s="65" t="s">
         <v>75</v>
       </c>
@@ -15285,7 +15305,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -15346,7 +15366,7 @@
       <c r="AG3" s="60"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49">
       <c r="A4" s="17">
         <f>+A3+1</f>
         <v>2</v>
@@ -15447,7 +15467,7 @@
       <c r="AG4" s="60"/>
       <c r="AT4" s="15"/>
     </row>
-    <row r="5" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49">
       <c r="A5" s="17">
         <f t="shared" ref="A5:A31" si="4">+A4+1</f>
         <v>3</v>
@@ -15505,7 +15525,7 @@
       <c r="AF5" s="65"/>
       <c r="AG5" s="60"/>
     </row>
-    <row r="6" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49">
       <c r="A6" s="17">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -15563,7 +15583,7 @@
       <c r="AF6" s="65"/>
       <c r="AG6" s="60"/>
     </row>
-    <row r="7" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49">
       <c r="A7" s="17">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -15676,7 +15696,7 @@
         <v>69700</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49">
       <c r="A8" s="17">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -15734,7 +15754,7 @@
       <c r="AF8" s="65"/>
       <c r="AG8" s="19"/>
     </row>
-    <row r="9" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49">
       <c r="A9" s="17">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -15795,7 +15815,7 @@
       <c r="AF9" s="65"/>
       <c r="AG9" s="19"/>
     </row>
-    <row r="10" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49">
       <c r="A10" s="17"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39" t="s">
@@ -15851,7 +15871,7 @@
       <c r="AF10" s="65"/>
       <c r="AG10" s="19"/>
     </row>
-    <row r="11" spans="1:49" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" s="8" customFormat="1">
       <c r="A11" s="37">
         <v>8</v>
       </c>
@@ -15941,7 +15961,7 @@
       <c r="AF11" s="37"/>
       <c r="AG11" s="38"/>
     </row>
-    <row r="12" spans="1:49" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" s="8" customFormat="1">
       <c r="A12" s="37">
         <f>+A11+1</f>
         <v>9</v>
@@ -16043,7 +16063,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49">
       <c r="A13" s="7">
         <f>+A12+1</f>
         <v>10</v>
@@ -16102,7 +16122,7 @@
       <c r="AF13" s="65"/>
       <c r="AG13" s="22"/>
     </row>
-    <row r="14" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49">
       <c r="A14" s="7">
         <f t="shared" ref="A14:A16" si="6">+A13+1</f>
         <v>11</v>
@@ -16160,7 +16180,7 @@
       <c r="AF14" s="65"/>
       <c r="AG14" s="22"/>
     </row>
-    <row r="15" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49">
       <c r="A15" s="7">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -16268,7 +16288,7 @@
       </c>
       <c r="AU15" s="15"/>
     </row>
-    <row r="16" spans="1:49" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49">
       <c r="A16" s="7">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -16370,7 +16390,7 @@
       </c>
       <c r="AT16" s="8"/>
     </row>
-    <row r="17" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48">
       <c r="A17" s="23">
         <f>+A16+1</f>
         <v>14</v>
@@ -16429,7 +16449,7 @@
       <c r="AF17" s="65"/>
       <c r="AG17" s="25"/>
     </row>
-    <row r="18" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48">
       <c r="A18" s="23">
         <f t="shared" ref="A18:A22" si="7">+A17+1</f>
         <v>15</v>
@@ -16487,7 +16507,7 @@
       <c r="AF18" s="65"/>
       <c r="AG18" s="25"/>
     </row>
-    <row r="19" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48">
       <c r="A19" s="23">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -16596,7 +16616,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48">
       <c r="A20" s="23">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -16686,7 +16706,7 @@
       <c r="AF20" s="65"/>
       <c r="AG20" s="25"/>
     </row>
-    <row r="21" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48">
       <c r="A21" s="23">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -16794,7 +16814,7 @@
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
     </row>
-    <row r="22" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48">
       <c r="A22" s="23">
         <f t="shared" si="7"/>
         <v>19</v>
@@ -16885,7 +16905,7 @@
       <c r="AF22" s="65"/>
       <c r="AG22" s="25"/>
     </row>
-    <row r="23" spans="1:48" s="8" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" s="8" customFormat="1">
       <c r="A23" s="11">
         <f>+A22+1</f>
         <v>20</v>
@@ -16994,7 +17014,7 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48">
       <c r="A24" s="11">
         <f t="shared" ref="A24:A29" si="8">+A23+1</f>
         <v>21</v>
@@ -17053,7 +17073,7 @@
       <c r="AG24" s="14"/>
       <c r="AN24" s="8"/>
     </row>
-    <row r="25" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48">
       <c r="A25" s="11">
         <f t="shared" si="8"/>
         <v>22</v>
@@ -17152,7 +17172,7 @@
         <v>13760</v>
       </c>
     </row>
-    <row r="26" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48">
       <c r="A26" s="11">
         <f t="shared" si="8"/>
         <v>23</v>
@@ -17212,7 +17232,7 @@
       <c r="AF26" s="65"/>
       <c r="AG26" s="14"/>
     </row>
-    <row r="27" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48">
       <c r="A27" s="11">
         <f t="shared" si="8"/>
         <v>24</v>
@@ -17324,7 +17344,7 @@
         <v>43400</v>
       </c>
     </row>
-    <row r="28" spans="1:48" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="15.6" customHeight="1">
       <c r="A28" s="11">
         <f t="shared" si="8"/>
         <v>25</v>
@@ -17382,7 +17402,7 @@
       <c r="AF28" s="65"/>
       <c r="AG28" s="14"/>
     </row>
-    <row r="29" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48">
       <c r="A29" s="11">
         <f t="shared" si="8"/>
         <v>26</v>
@@ -17488,7 +17508,7 @@
       </c>
       <c r="AH29" s="5"/>
     </row>
-    <row r="30" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48">
       <c r="A30" s="28">
         <f>+A29+1</f>
         <v>27</v>
@@ -17574,7 +17594,7 @@
       <c r="AG30" s="30"/>
       <c r="AH30" s="5"/>
     </row>
-    <row r="31" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48">
       <c r="A31" s="28">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -17635,7 +17655,7 @@
       <c r="AG31" s="30"/>
       <c r="AU31" s="5"/>
     </row>
-    <row r="32" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48">
       <c r="A32" s="28">
         <f>+A30+1</f>
         <v>28</v>
@@ -17694,7 +17714,7 @@
       <c r="AG32" s="30"/>
       <c r="AU32" s="5"/>
     </row>
-    <row r="33" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48">
       <c r="A33" s="28"/>
       <c r="B33" s="31">
         <v>10007050</v>
@@ -17773,7 +17793,7 @@
       <c r="AG33" s="30"/>
       <c r="AU33" s="5"/>
     </row>
-    <row r="34" spans="1:48" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" ht="18.600000000000001" customHeight="1">
       <c r="A34" s="28">
         <f>+A31+1</f>
         <v>29</v>
@@ -17834,7 +17854,7 @@
       <c r="AF34" s="65"/>
       <c r="AG34" s="30"/>
     </row>
-    <row r="35" spans="1:48" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="18.600000000000001" customHeight="1">
       <c r="A35" s="28">
         <f>+A32+1</f>
         <v>29</v>
@@ -17906,7 +17926,7 @@
       <c r="AF35" s="65"/>
       <c r="AG35" s="30"/>
     </row>
-    <row r="36" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48">
       <c r="A36" s="28">
         <f t="shared" ref="A36:A37" si="10">+A34+1</f>
         <v>30</v>
@@ -17962,7 +17982,7 @@
       <c r="AF36" s="65"/>
       <c r="AG36" s="30"/>
     </row>
-    <row r="37" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48">
       <c r="A37" s="28">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -18018,7 +18038,7 @@
       <c r="AF37" s="65"/>
       <c r="AG37" s="30"/>
     </row>
-    <row r="38" spans="1:48" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" s="15" customFormat="1">
       <c r="A38" s="23">
         <f>+A37+1</f>
         <v>31</v>
@@ -18099,7 +18119,7 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" spans="1:48" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" s="15" customFormat="1">
       <c r="A39" s="23">
         <f t="shared" ref="A39" si="11">+A38+1</f>
         <v>32</v>
@@ -18178,7 +18198,7 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" spans="1:48" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" s="15" customFormat="1">
       <c r="A40" s="48">
         <f>+A39+1</f>
         <v>33</v>
@@ -18237,7 +18257,7 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" spans="1:48" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" s="15" customFormat="1">
       <c r="A41" s="48">
         <f t="shared" ref="A41:A42" si="12">+A40+1</f>
         <v>34</v>
@@ -18296,7 +18316,7 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" spans="1:48" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" s="15" customFormat="1">
       <c r="A42" s="48">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -18355,7 +18375,7 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" spans="1:48" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48">
       <c r="A43" s="43">
         <f>+A42+1</f>
         <v>36</v>
@@ -18413,7 +18433,7 @@
       <c r="AF43" s="65"/>
       <c r="AG43" s="42"/>
     </row>
-    <row r="44" spans="1:48" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="3.6" customHeight="1">
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -18440,7 +18460,7 @@
       <c r="AA44" s="5"/>
       <c r="AB44" s="27"/>
     </row>
-    <row r="45" spans="1:48" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="15.75">
       <c r="C45" s="1" t="s">
         <v>92</v>
       </c>
@@ -18570,22 +18590,22 @@
         <v>-1656565.8</v>
       </c>
     </row>
-    <row r="46" spans="1:48" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="3.6" customHeight="1">
       <c r="AB46" s="27"/>
       <c r="AD46" s="5"/>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48">
       <c r="D47" s="74"/>
       <c r="AD47" s="5"/>
       <c r="AG47" s="5"/>
     </row>
-    <row r="48" spans="1:48" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:48">
       <c r="D48" s="5"/>
-      <c r="X48" s="96" t="s">
+      <c r="X48" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="Y48" s="97"/>
-      <c r="Z48" s="97"/>
+      <c r="Y48" s="128"/>
+      <c r="Z48" s="128"/>
       <c r="AA48" s="62">
         <f>+AA45/1000</f>
         <v>1656.5658000000001</v>
@@ -18597,7 +18617,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="24:33">
       <c r="X49" s="3" t="s">
         <v>70</v>
       </c>
@@ -18615,7 +18635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="24:33">
       <c r="Y50" s="61"/>
       <c r="Z50" s="61"/>
       <c r="AA50" s="63"/>
@@ -18627,7 +18647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="24:33">
       <c r="Y51" s="61"/>
       <c r="Z51" s="61"/>
       <c r="AA51" s="63"/>
@@ -18643,12 +18663,12 @@
         <v>404.6</v>
       </c>
     </row>
-    <row r="52" spans="24:33" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="X52" s="96" t="s">
+    <row r="52" spans="24:33">
+      <c r="X52" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="Y52" s="97"/>
-      <c r="Z52" s="97"/>
+      <c r="Y52" s="128"/>
+      <c r="Z52" s="128"/>
       <c r="AA52" s="64">
         <f>+AA48-AA49-AA50-AA51</f>
         <v>1656.5658000000001</v>
@@ -18659,17 +18679,17 @@
         <v>404.88</v>
       </c>
     </row>
-    <row r="53" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="24:33">
       <c r="AD53" s="63"/>
       <c r="AE53" s="63"/>
     </row>
-    <row r="54" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="24:33">
       <c r="AE54" s="63"/>
     </row>
-    <row r="55" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="24:33">
       <c r="Y55" s="5"/>
     </row>
-    <row r="56" spans="24:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="24:33">
       <c r="Y56" s="5"/>
       <c r="AA56" s="63"/>
     </row>
@@ -18693,19 +18713,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEFCDAC-5B36-4823-B79F-3948F56C00BD}">
   <dimension ref="B3:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="99" t="s">
+    <row r="3" spans="2:4">
+      <c r="B3" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4">
       <c r="B4" s="92" t="s">
         <v>100</v>
       </c>
@@ -18717,7 +18737,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4">
       <c r="B5" s="92" t="s">
         <v>101</v>
       </c>
@@ -18729,7 +18749,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4">
       <c r="B6" s="92" t="s">
         <v>102</v>
       </c>
@@ -18741,7 +18761,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4">
       <c r="C7" s="93">
         <f>SUM(C4:C6)</f>
         <v>5127857</v>

--- a/INPUT/inventario PT al 30-03-2026.xlsx
+++ b/INPUT/inventario PT al 30-03-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Downloads\INPUT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8961705-7AB9-49AB-8996-46A640B20E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CF6EB7-FE99-474C-82DB-DA87C516E199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{E49F44D6-2AA4-4DB6-B5AA-2D3E646476D9}"/>
   </bookViews>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="120">
   <si>
     <t>MATERIAL</t>
   </si>
@@ -403,9 +403,6 @@
     <t>STOCK AL ENE 2026</t>
   </si>
   <si>
-    <t>STOCK A MARZO 2026</t>
-  </si>
-  <si>
     <t>STOCK AL DIA FEBRERO 2026</t>
   </si>
   <si>
@@ -485,9 +482,6 @@
   </si>
   <si>
     <t>TM en Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -3144,56 +3138,56 @@
         <v>4</v>
       </c>
       <c r="AS2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT2" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="AU2" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV2" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW2" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="AT2" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU2" s="94" t="s">
+      <c r="AX2" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="118" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ2" s="118" t="s">
+        <v>109</v>
+      </c>
+      <c r="BA2" s="118" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB2" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="AV2" s="117" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW2" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="AX2" s="118" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY2" s="118" t="s">
-        <v>109</v>
-      </c>
-      <c r="AZ2" s="118" t="s">
-        <v>110</v>
-      </c>
-      <c r="BA2" s="118" t="s">
+      <c r="BC2" s="119" t="s">
         <v>111</v>
       </c>
-      <c r="BB2" s="118" t="s">
+      <c r="BD2" s="120" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="119" t="s">
-        <v>112</v>
-      </c>
-      <c r="BD2" s="120" t="s">
-        <v>116</v>
-      </c>
       <c r="BE2" s="120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BF2" s="121"/>
       <c r="BG2" s="122" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BH2" s="123" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BI2" s="122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BJ2" s="124" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:62">
@@ -3604,9 +3598,6 @@
       <c r="AP5" s="77">
         <f t="shared" si="2"/>
         <v>20</v>
-      </c>
-      <c r="AR5" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="AS5" s="3">
         <v>10009178</v>
@@ -5180,7 +5171,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" s="55">
         <v>331000</v>
@@ -9318,7 +9309,7 @@
       <c r="A41" s="23"/>
       <c r="B41" s="32"/>
       <c r="C41" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" s="56">
         <v>0</v>
@@ -9443,7 +9434,7 @@
       <c r="A42" s="23"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="56">
         <v>0</v>
@@ -10148,37 +10139,14 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="16.5" thickBot="1">
-      <c r="C48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" s="6">
-        <f>SUM(D3:D46)</f>
-        <v>2167722.7999999998</v>
-      </c>
-      <c r="E48" s="6">
-        <f>SUM(E3:E38)</f>
-        <v>70560</v>
-      </c>
-      <c r="F48" s="6">
-        <f>SUM(F3:F46)</f>
-        <v>96575</v>
-      </c>
-      <c r="G48" s="6">
-        <f>SUM(G3:G46)</f>
-        <v>28570</v>
-      </c>
-      <c r="H48" s="6">
-        <f>SUM(H3:H46)</f>
-        <v>9300</v>
-      </c>
-      <c r="I48" s="6">
-        <f t="shared" ref="I48:J48" si="30">SUM(I3:I46)</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="6">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
@@ -10196,30 +10164,12 @@
       <c r="Y48" s="6"/>
       <c r="Z48" s="6"/>
       <c r="AA48" s="6"/>
-      <c r="AB48" s="6">
-        <f>SUM(AB3:AB46)</f>
-        <v>0</v>
-      </c>
-      <c r="AC48" s="5">
-        <f>SUM(AC3:AC38)</f>
-        <v>0</v>
-      </c>
-      <c r="AD48" s="6">
-        <f>SUM(AD3:AD46)</f>
-        <v>2165902.7999999998</v>
-      </c>
-      <c r="AE48" s="6">
-        <f>SUM(AE3:AE46)</f>
-        <v>1440651</v>
-      </c>
-      <c r="AF48" s="73">
-        <f>SUM(AF3:AF46)</f>
-        <v>1728695</v>
-      </c>
-      <c r="AG48" s="35">
-        <f>SUM(AG3:AG47)</f>
-        <v>1877858.8</v>
-      </c>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="5"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="73"/>
+      <c r="AG48" s="35"/>
       <c r="AH48" s="27"/>
       <c r="AI48" s="9">
         <f>SUM(AI1:AI46)</f>
@@ -10246,7 +10196,7 @@
         <v>642576.80000000005</v>
       </c>
       <c r="AT48" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AU48" s="15"/>
       <c r="AV48" s="109">
@@ -10313,23 +10263,23 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5">
         <f>+AF48-AL50</f>
-        <v>1728695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="4:41">
       <c r="D51" s="5"/>
       <c r="E51" s="5">
         <f>+E48+F48</f>
-        <v>167135</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="127" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AE51" s="128"/>
       <c r="AF51" s="128"/>
       <c r="AG51" s="62">
         <f>ROUND(+AG48/1000,0)</f>
-        <v>1878</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="5" t="s">
         <v>71</v>
@@ -10430,7 +10380,7 @@
       <c r="AF55" s="128"/>
       <c r="AG55" s="64">
         <f>+AG51-AG52-AG53-AG54</f>
-        <v>1554</v>
+        <v>-324</v>
       </c>
       <c r="AJ55" s="63"/>
       <c r="AK55" s="3">
@@ -10442,9 +10392,6 @@
       </c>
     </row>
     <row r="56" spans="4:41">
-      <c r="AG56" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ56" s="63"/>
       <c r="AK56" s="63"/>
     </row>
@@ -14832,7 +14779,7 @@
     </row>
     <row r="46" spans="1:61" ht="15.75">
       <c r="C46" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D46" s="6">
         <f>SUM(D3:D44)</f>
@@ -15012,7 +14959,7 @@
     <row r="49" spans="4:44">
       <c r="D49" s="5"/>
       <c r="AG49" s="127" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH49" s="128"/>
       <c r="AI49" s="128"/>
@@ -18720,54 +18667,54 @@
   <sheetData>
     <row r="3" spans="2:4">
       <c r="B3" s="130" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="130"/>
       <c r="D3" s="130"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="93">
         <f>+Enero2026!Y45</f>
         <v>1418869</v>
       </c>
       <c r="D4" s="92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="93">
         <f>+Febrero2026!AH46</f>
         <v>2268337</v>
       </c>
       <c r="D5" s="92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="93">
         <f>+Marzo2026!AE48</f>
-        <v>1440651</v>
+        <v>0</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" s="93">
         <f>SUM(C4:C6)</f>
-        <v>5127857</v>
+        <v>3687206</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
